--- a/research/traditional_assets/database/data/macau/macau_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/macau/macau_hotel_gaming.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="sehk_1128" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,34 +590,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.165</v>
+        <v>-0.1485</v>
       </c>
       <c r="G2">
-        <v>0.02590200034062642</v>
+        <v>-0.1323443915792218</v>
       </c>
       <c r="H2">
-        <v>0.02590200034062642</v>
+        <v>-0.1323443915792218</v>
       </c>
       <c r="I2">
-        <v>-0.4553935314563698</v>
+        <v>-0.009440656977123119</v>
       </c>
       <c r="J2">
-        <v>-0.4553935314563698</v>
+        <v>-0.009440656977123119</v>
       </c>
       <c r="K2">
-        <v>-3034.07</v>
+        <v>-1174.053</v>
       </c>
       <c r="L2">
-        <v>-0.7278059101082089</v>
+        <v>-0.1530408655412892</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>4.733526720151473e-05</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.001328730474688962</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,76 +629,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.56</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>1659.89</v>
+        <v>1688.5</v>
       </c>
       <c r="V2">
-        <v>0.04455685805015931</v>
+        <v>0.0512343581216395</v>
       </c>
       <c r="W2">
-        <v>-1.362603550295858</v>
+        <v>-4.976923076923077</v>
       </c>
       <c r="X2">
-        <v>0.1038055742896521</v>
+        <v>0.09120621285540292</v>
       </c>
       <c r="Y2">
-        <v>-1.46640912458551</v>
+        <v>-5.06812928977848</v>
       </c>
       <c r="Z2">
-        <v>0.3410834383335242</v>
+        <v>0.6558065142107796</v>
       </c>
       <c r="AA2">
-        <v>-0.1198687448728466</v>
+        <v>-0.01969092721834496</v>
       </c>
       <c r="AB2">
-        <v>0.09105251795945217</v>
+        <v>0.07955927859530898</v>
       </c>
       <c r="AC2">
-        <v>-0.2203905879345398</v>
+        <v>-0.09810672191964734</v>
       </c>
       <c r="AD2">
-        <v>12892.37</v>
+        <v>12821.066</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>12892.37</v>
+        <v>12821.066</v>
       </c>
       <c r="AG2">
-        <v>11232.48</v>
+        <v>11132.566</v>
       </c>
       <c r="AH2">
-        <v>0.2570983696099783</v>
+        <v>0.2800737375895818</v>
       </c>
       <c r="AI2">
-        <v>0.9647009789653034</v>
+        <v>1.038507440586842</v>
       </c>
       <c r="AJ2">
-        <v>0.2316654491275586</v>
+        <v>0.2525023154319382</v>
       </c>
       <c r="AK2">
-        <v>0.959694879282857</v>
+        <v>1.044608482217505</v>
       </c>
       <c r="AL2">
-        <v>860.6510000000001</v>
+        <v>1196.734</v>
       </c>
       <c r="AM2">
-        <v>850.162</v>
+        <v>1080.16</v>
       </c>
       <c r="AN2">
-        <v>-22.05565763047056</v>
+        <v>10.88587339983749</v>
       </c>
       <c r="AO2">
-        <v>-2.205818618696777</v>
+        <v>-0.06051804327444529</v>
       </c>
       <c r="AP2">
-        <v>-19.2159962226579</v>
+        <v>9.452233074171465</v>
       </c>
       <c r="AQ2">
-        <v>-2.233033233666054</v>
+        <v>-0.06704932602577397</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +712,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sands China Ltd. (SEHK:1928)</t>
+          <t>Wynn Macau, Limited (SEHK:1128)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +721,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.213</v>
+        <v>-0.144</v>
       </c>
       <c r="G3">
-        <v>0.09266943291839558</v>
+        <v>-0.1321356615177972</v>
       </c>
       <c r="H3">
-        <v>0.09266943291839558</v>
+        <v>-0.1321356615177972</v>
       </c>
       <c r="I3">
-        <v>-0.4038727524204703</v>
+        <v>0.06283579583613162</v>
       </c>
       <c r="J3">
-        <v>-0.4038727524204703</v>
+        <v>0.06283579583613162</v>
       </c>
       <c r="K3">
-        <v>-1427</v>
+        <v>-231.9</v>
       </c>
       <c r="L3">
-        <v>-0.6579068695251268</v>
+        <v>-0.09733881799865682</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +763,52 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>766</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.0284939496854878</v>
-      </c>
-      <c r="W3">
-        <v>-0.913572343149808</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.1038055742896521</v>
-      </c>
-      <c r="Y3">
-        <v>-1.01737791743946</v>
-      </c>
-      <c r="Z3">
-        <v>0.2621464829586657</v>
-      </c>
-      <c r="AA3">
-        <v>-0.1058738216098622</v>
+        <v>0.07976796867019348</v>
       </c>
       <c r="AB3">
-        <v>0.0917413743032281</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1976151959130903</v>
+        <v>0.07976796867019348</v>
       </c>
       <c r="AD3">
-        <v>8660</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8660</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>7894</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>0.2436492238956303</v>
-      </c>
-      <c r="AI3">
-        <v>0.9852104664391353</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.2269897546934891</v>
-      </c>
-      <c r="AK3">
-        <v>0.9837986041874377</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>360</v>
+        <v>407.6</v>
       </c>
       <c r="AM3">
-        <v>358</v>
+        <v>352.1</v>
       </c>
       <c r="AN3">
-        <v>-53.12883435582822</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>-2.433333333333333</v>
+        <v>0.3672718351324828</v>
       </c>
       <c r="AP3">
-        <v>-48.42944785276074</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-2.446927374301676</v>
+        <v>0.4251633058790116</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +819,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Macau Legend Development Limited (SEHK:1680)</t>
+          <t>MGM China Holdings Limited (SEHK:2282)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,34 +828,34 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0706</v>
+        <v>-0.0517</v>
       </c>
       <c r="G4">
-        <v>-0.337874659400545</v>
+        <v>-0.1288173237090505</v>
       </c>
       <c r="H4">
-        <v>-0.337874659400545</v>
+        <v>-0.1288173237090505</v>
       </c>
       <c r="I4">
-        <v>-0.7009536784741144</v>
+        <v>-0.01091985933740514</v>
       </c>
       <c r="J4">
-        <v>-0.7009536784741144</v>
+        <v>-0.01091985933740514</v>
       </c>
       <c r="K4">
-        <v>-125.8</v>
+        <v>-256.1</v>
       </c>
       <c r="L4">
-        <v>-0.8569482288828337</v>
+        <v>-0.1579986427293479</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>1.56</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.0003236111687341825</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0.006091370558375634</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -883,76 +867,79 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.56</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>8.390000000000001</v>
+        <v>448.4</v>
       </c>
       <c r="V4">
-        <v>0.02637535366237032</v>
+        <v>0.09301746670538937</v>
       </c>
       <c r="W4">
-        <v>-0.2028377942599161</v>
+        <v>1.692663582286847</v>
       </c>
       <c r="X4">
-        <v>0.1333322825280632</v>
+        <v>0.1011354646516523</v>
       </c>
       <c r="Y4">
-        <v>-0.3361700767879793</v>
+        <v>1.591528117635195</v>
       </c>
       <c r="Z4">
-        <v>0.1629843455090485</v>
+        <v>0.5670853304411714</v>
       </c>
       <c r="AA4">
-        <v>-0.1142444765182636</v>
+        <v>-0.006192492040723507</v>
       </c>
       <c r="AB4">
-        <v>0.09105251795945217</v>
+        <v>0.08239640561092618</v>
       </c>
       <c r="AC4">
-        <v>-0.2052969944777157</v>
+        <v>-0.08858889765164968</v>
       </c>
       <c r="AD4">
-        <v>336.2</v>
+        <v>3437.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>336.2</v>
+        <v>3437.6</v>
       </c>
       <c r="AG4">
-        <v>327.81</v>
+        <v>2989.2</v>
       </c>
       <c r="AH4">
-        <v>0.5138315757297875</v>
+        <v>0.4162650456515947</v>
       </c>
       <c r="AI4">
-        <v>0.408059230489137</v>
+        <v>1.132988365577931</v>
       </c>
       <c r="AJ4">
-        <v>0.5075165270703348</v>
+        <v>0.3827498783579605</v>
       </c>
       <c r="AK4">
-        <v>0.4019693198121421</v>
+        <v>1.156050585914839</v>
       </c>
       <c r="AL4">
-        <v>10.8</v>
+        <v>236.7</v>
       </c>
       <c r="AM4">
-        <v>8.690000000000001</v>
+        <v>222</v>
       </c>
       <c r="AN4">
-        <v>-6.477842003853564</v>
+        <v>15.34642857142857</v>
       </c>
       <c r="AO4">
-        <v>-9.527777777777777</v>
+        <v>-0.07477820025348543</v>
       </c>
       <c r="AP4">
-        <v>-6.316184971098266</v>
+        <v>13.34464285714286</v>
       </c>
       <c r="AQ4">
-        <v>-11.84119677790564</v>
+        <v>-0.07972972972972972</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +950,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MGM China Holdings Limited (SEHK:2282)</t>
+          <t>Sands China Ltd. (SEHK:1928)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -972,25 +959,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.117</v>
+        <v>-0.153</v>
       </c>
       <c r="G5">
-        <v>-0.03073262615247348</v>
+        <v>-0.1263598326359833</v>
       </c>
       <c r="H5">
-        <v>-0.03073262615247348</v>
+        <v>-0.1263598326359833</v>
       </c>
       <c r="I5">
-        <v>-0.3621493010805988</v>
+        <v>-0.04407252440725244</v>
       </c>
       <c r="J5">
-        <v>-0.3621493010805988</v>
+        <v>-0.04407252440725244</v>
       </c>
       <c r="K5">
-        <v>-575.7</v>
+        <v>-647</v>
       </c>
       <c r="L5">
-        <v>-0.5707346089025479</v>
+        <v>-0.1804741980474198</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1014,73 +1001,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>885.5</v>
+        <v>1228</v>
       </c>
       <c r="V5">
-        <v>0.2112760068715404</v>
+        <v>0.05187212760205461</v>
       </c>
       <c r="W5">
-        <v>-1.362603550295858</v>
+        <v>-4.976923076923077</v>
       </c>
       <c r="X5">
-        <v>0.1282067030237747</v>
+        <v>0.09120621285540292</v>
       </c>
       <c r="Y5">
-        <v>-1.490810253319633</v>
+        <v>-5.06812928977848</v>
       </c>
       <c r="Z5">
-        <v>0.3309926168990976</v>
+        <v>0.4467846460618146</v>
       </c>
       <c r="AA5">
-        <v>-0.1198687448728466</v>
+        <v>-0.01969092721834496</v>
       </c>
       <c r="AB5">
-        <v>0.1005218430616932</v>
+        <v>0.07841579470130237</v>
       </c>
       <c r="AC5">
-        <v>-0.2203905879345398</v>
+        <v>-0.09810672191964734</v>
       </c>
       <c r="AD5">
-        <v>3895.1</v>
+        <v>9037</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>3895.1</v>
+        <v>9037</v>
       </c>
       <c r="AG5">
-        <v>3009.6</v>
+        <v>7809</v>
       </c>
       <c r="AH5">
-        <v>0.4816912555804262</v>
+        <v>0.2762713004347215</v>
       </c>
       <c r="AI5">
-        <v>1.040413483626262</v>
+        <v>1.061802373399131</v>
       </c>
       <c r="AJ5">
-        <v>0.4179535607154761</v>
+        <v>0.2480417754569191</v>
       </c>
       <c r="AK5">
-        <v>1.052933561907428</v>
+        <v>1.07222298503364</v>
       </c>
       <c r="AL5">
-        <v>182.7</v>
+        <v>533</v>
       </c>
       <c r="AM5">
-        <v>182.134</v>
+        <v>488</v>
       </c>
       <c r="AN5">
-        <v>-36.99050332383666</v>
+        <v>16.19534050179211</v>
       </c>
       <c r="AO5">
-        <v>-1.999452654625069</v>
+        <v>-0.2964352720450281</v>
       </c>
       <c r="AP5">
-        <v>-28.58119658119658</v>
+        <v>13.99462365591398</v>
       </c>
       <c r="AQ5">
-        <v>-2.005666157883756</v>
+        <v>-0.3237704918032787</v>
       </c>
     </row>
     <row r="6">
@@ -1091,7 +1078,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wynn Macau, Limited (SEHK:1128)</t>
+          <t>Macau Legend Development Limited (SEHK:1680)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1100,25 +1087,25 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.275</v>
+        <v>-0.212</v>
       </c>
       <c r="G6">
-        <v>-0.01317507418397626</v>
+        <v>-0.4973333333333333</v>
       </c>
       <c r="H6">
-        <v>-0.01317507418397626</v>
+        <v>-0.4973333333333333</v>
       </c>
       <c r="I6">
-        <v>-0.6561424332344213</v>
+        <v>-0.616</v>
       </c>
       <c r="J6">
-        <v>-0.6561424332344213</v>
+        <v>-0.616</v>
       </c>
       <c r="K6">
-        <v>-903.2</v>
+        <v>-38.8</v>
       </c>
       <c r="L6">
-        <v>-1.072047477744807</v>
+        <v>-0.5173333333333333</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1142,52 +1129,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>0.08153638814016172</v>
+      </c>
+      <c r="W6">
+        <v>-0.07955710477752717</v>
       </c>
       <c r="X6">
-        <v>0.09086034234937965</v>
+        <v>0.1495896776748042</v>
+      </c>
+      <c r="Y6">
+        <v>-0.2291467824523314</v>
+      </c>
+      <c r="Z6">
+        <v>0.09196698998172922</v>
+      </c>
+      <c r="AA6">
+        <v>-0.05665166582874521</v>
       </c>
       <c r="AB6">
-        <v>0.09086034234937965</v>
+        <v>0.07565342642617286</v>
+      </c>
+      <c r="AC6">
+        <v>-0.1323050922549181</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>345.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>345.8</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>333.7</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.6997167138810197</v>
+      </c>
+      <c r="AI6">
+        <v>0.4350232733677192</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>0.6921800456336858</v>
+      </c>
+      <c r="AK6">
+        <v>0.4262902401635156</v>
       </c>
       <c r="AL6">
-        <v>307.1</v>
+        <v>19.4</v>
       </c>
       <c r="AM6">
-        <v>301.29</v>
+        <v>18.03</v>
       </c>
       <c r="AN6">
-        <v>-0</v>
+        <v>-125.7454545454545</v>
       </c>
       <c r="AO6">
-        <v>-1.80006512536633</v>
+        <v>-2.381443298969073</v>
       </c>
       <c r="AP6">
-        <v>-0</v>
+        <v>-121.3454545454545</v>
       </c>
       <c r="AQ6">
-        <v>-1.834777125029041</v>
+        <v>-2.562396006655574</v>
       </c>
     </row>
     <row r="7">
@@ -1207,22 +1215,22 @@
         </is>
       </c>
       <c r="G7">
-        <v>-0.7374301675977654</v>
+        <v>-0.1682926829268293</v>
       </c>
       <c r="H7">
-        <v>-0.7374301675977654</v>
+        <v>-0.1682926829268293</v>
       </c>
       <c r="I7">
-        <v>-0.8044692737430167</v>
+        <v>-0.02731707317073171</v>
       </c>
       <c r="J7">
-        <v>-0.8044692737430167</v>
+        <v>-0.02731707317073171</v>
       </c>
       <c r="K7">
-        <v>-2.37</v>
+        <v>-0.253</v>
       </c>
       <c r="L7">
-        <v>-1.324022346368715</v>
+        <v>-0.03085365853658537</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1252,52 +1260,8821 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>0.09306538618207964</v>
+        <v>0.08087051041284887</v>
       </c>
       <c r="AB7">
-        <v>0.09087979715811985</v>
+        <v>0.07955927859530898</v>
       </c>
       <c r="AD7">
-        <v>1.07</v>
+        <v>0.666</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1.07</v>
+        <v>0.666</v>
       </c>
       <c r="AG7">
-        <v>1.07</v>
+        <v>0.666</v>
       </c>
       <c r="AH7">
-        <v>0.05201750121536218</v>
+        <v>0.03548971544282212</v>
       </c>
       <c r="AI7">
-        <v>0.1669266770670827</v>
+        <v>0.1175432403812213</v>
       </c>
       <c r="AJ7">
-        <v>0.05201750121536218</v>
+        <v>0.03548971544282212</v>
       </c>
       <c r="AK7">
-        <v>0.1669266770670827</v>
+        <v>0.1175432403812213</v>
       </c>
       <c r="AL7">
-        <v>0.051</v>
+        <v>0.034</v>
       </c>
       <c r="AM7">
-        <v>0.04799999999999999</v>
+        <v>0.03</v>
       </c>
       <c r="AN7">
-        <v>-1.276849642004773</v>
+        <v>31.71428571428572</v>
       </c>
       <c r="AO7">
-        <v>-28.23529411764706</v>
+        <v>-6.588235294117647</v>
       </c>
       <c r="AP7">
-        <v>-1.276849642004773</v>
+        <v>31.71428571428572</v>
       </c>
       <c r="AQ7">
-        <v>-30</v>
+        <v>-7.466666666666666</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Wynn Macau, Limited (SEHK:1128)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SEHK:1128</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hotel/Gaming</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Macau</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.235034347399411</v>
+      </c>
+      <c r="F2">
+        <v>4.85400989415927</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0.862373902132999</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.08</v>
+      </c>
+      <c r="K2">
+        <v>4295.7</v>
+      </c>
+      <c r="L2">
+        <v>3983.35881237488</v>
+      </c>
+      <c r="M2">
+        <v>4295.7</v>
+      </c>
+      <c r="N2">
+        <v>4327.01481237488</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>343.656</v>
+      </c>
+      <c r="Q2">
+        <v>0.07976796867019351</v>
+      </c>
+      <c r="R2">
+        <v>0.0791440094049824</v>
+      </c>
+      <c r="S2">
+        <v>0.0527107387696752</v>
+      </c>
+      <c r="T2">
+        <v>0.0420045055696752</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.07976796867019351</v>
+      </c>
+      <c r="X2">
+        <v>0.08237353147761781</v>
+      </c>
+      <c r="Y2">
+        <v>0.7480479046815171</v>
+      </c>
+      <c r="Z2">
+        <v>0.795623751419261</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0.07206827832878751</v>
+      </c>
+      <c r="AC2">
+        <v>0.2350343473994112</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>407.6</v>
+      </c>
+      <c r="AF2">
+        <v>302.7</v>
+      </c>
+      <c r="AG2">
+        <v>398.5</v>
+      </c>
+      <c r="AH2">
+        <v>0.006530278328787512</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>4295.7</v>
+      </c>
+      <c r="AK2">
+        <v>0.05476650414205181</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.2686</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>407.6</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.07976796867019348</v>
+      </c>
+      <c r="C2">
+        <v>4295.7</v>
+      </c>
+      <c r="D2">
+        <v>4295.7</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>4295.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>398.5</v>
+      </c>
+      <c r="K2">
+        <v>302.7</v>
+      </c>
+      <c r="L2">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="O2">
+        <v>25.73188</v>
+      </c>
+      <c r="P2">
+        <v>70.06812000000001</v>
+      </c>
+      <c r="Q2">
+        <v>372.76812</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.07976796867019348</v>
+      </c>
+      <c r="T2">
+        <v>0.7480479046815168</v>
+      </c>
+      <c r="U2">
+        <v>0.05123027832878752</v>
+      </c>
+      <c r="V2">
+        <v>0.2686</v>
+      </c>
+      <c r="W2">
+        <v>0.03746982556967519</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.07964462696204208</v>
+      </c>
+      <c r="C3">
+        <v>4258.89718912785</v>
+      </c>
+      <c r="D3">
+        <v>4301.85418912785</v>
+      </c>
+      <c r="E3">
+        <v>42.957</v>
+      </c>
+      <c r="F3">
+        <v>42.957</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>4295.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>398.5</v>
+      </c>
+      <c r="K3">
+        <v>302.7</v>
+      </c>
+      <c r="L3">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M3">
+        <v>2.200699066169725</v>
+      </c>
+      <c r="N3">
+        <v>93.59930093383029</v>
+      </c>
+      <c r="O3">
+        <v>25.14077223082682</v>
+      </c>
+      <c r="P3">
+        <v>68.45852870300348</v>
+      </c>
+      <c r="Q3">
+        <v>371.1585287030035</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08007063505691447</v>
+      </c>
+      <c r="T3">
+        <v>0.7535743919288306</v>
+      </c>
+      <c r="U3">
+        <v>0.05123027832878752</v>
+      </c>
+      <c r="V3">
+        <v>0.2686</v>
+      </c>
+      <c r="W3">
+        <v>0.03746982556967519</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>43.53162205259535</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.07952128525389068</v>
+      </c>
+      <c r="C4">
+        <v>4222.112037022147</v>
+      </c>
+      <c r="D4">
+        <v>4308.026037022147</v>
+      </c>
+      <c r="E4">
+        <v>85.914</v>
+      </c>
+      <c r="F4">
+        <v>85.914</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>4295.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>398.5</v>
+      </c>
+      <c r="K4">
+        <v>302.7</v>
+      </c>
+      <c r="L4">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M4">
+        <v>4.401398132339451</v>
+      </c>
+      <c r="N4">
+        <v>91.39860186766056</v>
+      </c>
+      <c r="O4">
+        <v>24.54966446165363</v>
+      </c>
+      <c r="P4">
+        <v>66.84893740600694</v>
+      </c>
+      <c r="Q4">
+        <v>369.5489374060069</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08037947830867059</v>
+      </c>
+      <c r="T4">
+        <v>0.759213664630171</v>
+      </c>
+      <c r="U4">
+        <v>0.05123027832878752</v>
+      </c>
+      <c r="V4">
+        <v>0.2686</v>
+      </c>
+      <c r="W4">
+        <v>0.03746982556967519</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>21.76581102629767</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.07939794354573931</v>
+      </c>
+      <c r="C5">
+        <v>4185.344619796914</v>
+      </c>
+      <c r="D5">
+        <v>4314.215619796914</v>
+      </c>
+      <c r="E5">
+        <v>128.871</v>
+      </c>
+      <c r="F5">
+        <v>128.871</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>4295.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>398.5</v>
+      </c>
+      <c r="K5">
+        <v>302.7</v>
+      </c>
+      <c r="L5">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M5">
+        <v>6.602097198509175</v>
+      </c>
+      <c r="N5">
+        <v>89.19790280149084</v>
+      </c>
+      <c r="O5">
+        <v>23.95855669248044</v>
+      </c>
+      <c r="P5">
+        <v>65.2393461090104</v>
+      </c>
+      <c r="Q5">
+        <v>367.9393461090104</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.0806946894625248</v>
+      </c>
+      <c r="T5">
+        <v>0.7649692109954569</v>
+      </c>
+      <c r="U5">
+        <v>0.05123027832878752</v>
+      </c>
+      <c r="V5">
+        <v>0.2686</v>
+      </c>
+      <c r="W5">
+        <v>0.03746982556967519</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>14.51054068419845</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.07930678343758792</v>
+      </c>
+      <c r="C6">
+        <v>4146.973695211148</v>
+      </c>
+      <c r="D6">
+        <v>4318.801695211148</v>
+      </c>
+      <c r="E6">
+        <v>171.828</v>
+      </c>
+      <c r="F6">
+        <v>171.828</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>4295.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>398.5</v>
+      </c>
+      <c r="K6">
+        <v>302.7</v>
+      </c>
+      <c r="L6">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M6">
+        <v>8.9918070646789</v>
+      </c>
+      <c r="N6">
+        <v>86.80819293532112</v>
+      </c>
+      <c r="O6">
+        <v>23.31668062242725</v>
+      </c>
+      <c r="P6">
+        <v>63.49151231289386</v>
+      </c>
+      <c r="Q6">
+        <v>366.1915123128938</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08101646751541762</v>
+      </c>
+      <c r="T6">
+        <v>0.7708446645766861</v>
+      </c>
+      <c r="U6">
+        <v>0.05233027832878751</v>
+      </c>
+      <c r="V6">
+        <v>0.2686</v>
+      </c>
+      <c r="W6">
+        <v>0.03827436556967519</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>10.65414318956154</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.07927194112943654</v>
+      </c>
+      <c r="C7">
+        <v>4105.772115774783</v>
+      </c>
+      <c r="D7">
+        <v>4320.557115774783</v>
+      </c>
+      <c r="E7">
+        <v>214.785</v>
+      </c>
+      <c r="F7">
+        <v>214.785</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>4295.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>398.5</v>
+      </c>
+      <c r="K7">
+        <v>302.7</v>
+      </c>
+      <c r="L7">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M7">
+        <v>11.71228583084863</v>
+      </c>
+      <c r="N7">
+        <v>84.08771416915138</v>
+      </c>
+      <c r="O7">
+        <v>22.58596002583406</v>
+      </c>
+      <c r="P7">
+        <v>61.50175414331732</v>
+      </c>
+      <c r="Q7">
+        <v>364.2017541433173</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08134501984310819</v>
+      </c>
+      <c r="T7">
+        <v>0.7768438119175202</v>
+      </c>
+      <c r="U7">
+        <v>0.05453027832878751</v>
+      </c>
+      <c r="V7">
+        <v>0.2686</v>
+      </c>
+      <c r="W7">
+        <v>0.03988344556967519</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>8.179445189740449</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.07923856162128515</v>
+      </c>
+      <c r="C8">
+        <v>4064.498176671405</v>
+      </c>
+      <c r="D8">
+        <v>4322.240176671406</v>
+      </c>
+      <c r="E8">
+        <v>257.742</v>
+      </c>
+      <c r="F8">
+        <v>257.742</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>4295.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>398.5</v>
+      </c>
+      <c r="K8">
+        <v>302.7</v>
+      </c>
+      <c r="L8">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M8">
+        <v>14.44135599701835</v>
+      </c>
+      <c r="N8">
+        <v>81.35864400298166</v>
+      </c>
+      <c r="O8">
+        <v>21.85293177920088</v>
+      </c>
+      <c r="P8">
+        <v>59.50571222378079</v>
+      </c>
+      <c r="Q8">
+        <v>362.2057122237808</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08168056264585599</v>
+      </c>
+      <c r="T8">
+        <v>0.7829706006911378</v>
+      </c>
+      <c r="U8">
+        <v>0.05603027832878751</v>
+      </c>
+      <c r="V8">
+        <v>0.2686</v>
+      </c>
+      <c r="W8">
+        <v>0.04098054556967519</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>6.633726086371631</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.07922200431313377</v>
+      </c>
+      <c r="C9">
+        <v>4022.376515559104</v>
+      </c>
+      <c r="D9">
+        <v>4323.075515559104</v>
+      </c>
+      <c r="E9">
+        <v>300.699</v>
+      </c>
+      <c r="F9">
+        <v>300.699</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>4295.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>398.5</v>
+      </c>
+      <c r="K9">
+        <v>302.7</v>
+      </c>
+      <c r="L9">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M9">
+        <v>17.26922726318808</v>
+      </c>
+      <c r="N9">
+        <v>78.53077273681194</v>
+      </c>
+      <c r="O9">
+        <v>21.09336555710769</v>
+      </c>
+      <c r="P9">
+        <v>57.43740717970425</v>
+      </c>
+      <c r="Q9">
+        <v>360.1374071797043</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08202332142285645</v>
+      </c>
+      <c r="T9">
+        <v>0.789229148363113</v>
+      </c>
+      <c r="U9">
+        <v>0.05743027832878751</v>
+      </c>
+      <c r="V9">
+        <v>0.2686</v>
+      </c>
+      <c r="W9">
+        <v>0.04200450556967519</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>5.54743987903917</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.07914400940498237</v>
+      </c>
+      <c r="C10">
+        <v>3983.358812374879</v>
+      </c>
+      <c r="D10">
+        <v>4327.014812374879</v>
+      </c>
+      <c r="E10">
+        <v>343.656</v>
+      </c>
+      <c r="F10">
+        <v>343.656</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>4295.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>398.5</v>
+      </c>
+      <c r="K10">
+        <v>302.7</v>
+      </c>
+      <c r="L10">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M10">
+        <v>19.7362597293578</v>
+      </c>
+      <c r="N10">
+        <v>76.06374027064221</v>
+      </c>
+      <c r="O10">
+        <v>20.4307206366945</v>
+      </c>
+      <c r="P10">
+        <v>55.63301963394771</v>
+      </c>
+      <c r="Q10">
+        <v>358.3330196339477</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08237353147761778</v>
+      </c>
+      <c r="T10">
+        <v>0.7956237514192613</v>
+      </c>
+      <c r="U10">
+        <v>0.05743027832878751</v>
+      </c>
+      <c r="V10">
+        <v>0.2686</v>
+      </c>
+      <c r="W10">
+        <v>0.04200450556967519</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>4.854009894159274</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.07923716209683097</v>
+      </c>
+      <c r="C11">
+        <v>3935.697772107738</v>
+      </c>
+      <c r="D11">
+        <v>4322.310772107738</v>
+      </c>
+      <c r="E11">
+        <v>386.6129999999999</v>
+      </c>
+      <c r="F11">
+        <v>386.6129999999999</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>4295.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>398.5</v>
+      </c>
+      <c r="K11">
+        <v>302.7</v>
+      </c>
+      <c r="L11">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M11">
+        <v>23.20848599552752</v>
+      </c>
+      <c r="N11">
+        <v>72.59151400447249</v>
+      </c>
+      <c r="O11">
+        <v>19.49808066160131</v>
+      </c>
+      <c r="P11">
+        <v>53.09343334287118</v>
+      </c>
+      <c r="Q11">
+        <v>355.7934333428711</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08273143845665956</v>
+      </c>
+      <c r="T11">
+        <v>0.8021588952019184</v>
+      </c>
+      <c r="U11">
+        <v>0.06003027832878751</v>
+      </c>
+      <c r="V11">
+        <v>0.2686</v>
+      </c>
+      <c r="W11">
+        <v>0.04390614556967519</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>4.127800495838526</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.07937566158867958</v>
+      </c>
+      <c r="C12">
+        <v>3885.765679091073</v>
+      </c>
+      <c r="D12">
+        <v>4315.335679091073</v>
+      </c>
+      <c r="E12">
+        <v>429.57</v>
+      </c>
+      <c r="F12">
+        <v>429.57</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>4295.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>398.5</v>
+      </c>
+      <c r="K12">
+        <v>302.7</v>
+      </c>
+      <c r="L12">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M12">
+        <v>26.94704566169725</v>
+      </c>
+      <c r="N12">
+        <v>68.85295433830277</v>
+      </c>
+      <c r="O12">
+        <v>18.49390353526812</v>
+      </c>
+      <c r="P12">
+        <v>50.35905080303464</v>
+      </c>
+      <c r="Q12">
+        <v>353.0590508030346</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08309729892412451</v>
+      </c>
+      <c r="T12">
+        <v>0.8088392644019681</v>
+      </c>
+      <c r="U12">
+        <v>0.06273027832878751</v>
+      </c>
+      <c r="V12">
+        <v>0.2686</v>
+      </c>
+      <c r="W12">
+        <v>0.04588092556967519</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>3.555120706095471</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.07971456468052822</v>
+      </c>
+      <c r="C13">
+        <v>3825.835452884919</v>
+      </c>
+      <c r="D13">
+        <v>4298.362452884919</v>
+      </c>
+      <c r="E13">
+        <v>472.527</v>
+      </c>
+      <c r="F13">
+        <v>472.527</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>4295.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>398.5</v>
+      </c>
+      <c r="K13">
+        <v>302.7</v>
+      </c>
+      <c r="L13">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M13">
+        <v>31.86262712786697</v>
+      </c>
+      <c r="N13">
+        <v>63.93737287213304</v>
+      </c>
+      <c r="O13">
+        <v>17.17357835345494</v>
+      </c>
+      <c r="P13">
+        <v>46.7637945186781</v>
+      </c>
+      <c r="Q13">
+        <v>349.4637945186781</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08347138097512802</v>
+      </c>
+      <c r="T13">
+        <v>0.8156697542581985</v>
+      </c>
+      <c r="U13">
+        <v>0.06743027832878751</v>
+      </c>
+      <c r="V13">
+        <v>0.2686</v>
+      </c>
+      <c r="W13">
+        <v>0.04931850556967519</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>3.00665728583986</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08093846177237682</v>
+      </c>
+      <c r="C14">
+        <v>3722.678412511038</v>
+      </c>
+      <c r="D14">
+        <v>4238.162412511038</v>
+      </c>
+      <c r="E14">
+        <v>515.4839999999999</v>
+      </c>
+      <c r="F14">
+        <v>515.4839999999999</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>4295.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>398.5</v>
+      </c>
+      <c r="K14">
+        <v>302.7</v>
+      </c>
+      <c r="L14">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M14">
+        <v>41.9760055940367</v>
+      </c>
+      <c r="N14">
+        <v>53.82399440596331</v>
+      </c>
+      <c r="O14">
+        <v>14.45712489744175</v>
+      </c>
+      <c r="P14">
+        <v>39.36686950852157</v>
+      </c>
+      <c r="Q14">
+        <v>342.0668695085216</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08385396489092704</v>
+      </c>
+      <c r="T14">
+        <v>0.8226554825202526</v>
+      </c>
+      <c r="U14">
+        <v>0.08143027832878752</v>
+      </c>
+      <c r="V14">
+        <v>0.2686</v>
+      </c>
+      <c r="W14">
+        <v>0.0595581055696752</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>2.282256223388959</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08103600286422542</v>
+      </c>
+      <c r="C15">
+        <v>3674.996110501191</v>
+      </c>
+      <c r="D15">
+        <v>4233.437110501191</v>
+      </c>
+      <c r="E15">
+        <v>558.441</v>
+      </c>
+      <c r="F15">
+        <v>558.441</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>4295.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>398.5</v>
+      </c>
+      <c r="K15">
+        <v>302.7</v>
+      </c>
+      <c r="L15">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M15">
+        <v>45.47400606020643</v>
+      </c>
+      <c r="N15">
+        <v>50.32599393979358</v>
+      </c>
+      <c r="O15">
+        <v>13.51756197222855</v>
+      </c>
+      <c r="P15">
+        <v>36.80843196756502</v>
+      </c>
+      <c r="Q15">
+        <v>339.508431967565</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08424534383927317</v>
+      </c>
+      <c r="T15">
+        <v>0.8298018022366065</v>
+      </c>
+      <c r="U15">
+        <v>0.08143027832878752</v>
+      </c>
+      <c r="V15">
+        <v>0.2686</v>
+      </c>
+      <c r="W15">
+        <v>0.0595581055696752</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>2.106698052359039</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08280259875607404</v>
+      </c>
+      <c r="C16">
+        <v>3548.245223332327</v>
+      </c>
+      <c r="D16">
+        <v>4149.643223332327</v>
+      </c>
+      <c r="E16">
+        <v>601.398</v>
+      </c>
+      <c r="F16">
+        <v>601.398</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>4295.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>398.5</v>
+      </c>
+      <c r="K16">
+        <v>302.7</v>
+      </c>
+      <c r="L16">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M16">
+        <v>58.77479392637616</v>
+      </c>
+      <c r="N16">
+        <v>37.02520607362386</v>
+      </c>
+      <c r="O16">
+        <v>9.944970351375368</v>
+      </c>
+      <c r="P16">
+        <v>27.08023572224849</v>
+      </c>
+      <c r="Q16">
+        <v>329.7802357222484</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08464582462362734</v>
+      </c>
+      <c r="T16">
+        <v>0.837114315434736</v>
+      </c>
+      <c r="U16">
+        <v>0.09773027832878751</v>
+      </c>
+      <c r="V16">
+        <v>0.2686</v>
+      </c>
+      <c r="W16">
+        <v>0.0714799255696752</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>1.629950419222281</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08301935804792265</v>
+      </c>
+      <c r="C17">
+        <v>3495.234729097916</v>
+      </c>
+      <c r="D17">
+        <v>4139.589729097916</v>
+      </c>
+      <c r="E17">
+        <v>644.3549999999999</v>
+      </c>
+      <c r="F17">
+        <v>644.3549999999999</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>4295.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>398.5</v>
+      </c>
+      <c r="K17">
+        <v>302.7</v>
+      </c>
+      <c r="L17">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M17">
+        <v>62.97299349254587</v>
+      </c>
+      <c r="N17">
+        <v>32.82700650745414</v>
+      </c>
+      <c r="O17">
+        <v>8.817333947902183</v>
+      </c>
+      <c r="P17">
+        <v>24.00967255955196</v>
+      </c>
+      <c r="Q17">
+        <v>326.709672559552</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08505572848526044</v>
+      </c>
+      <c r="T17">
+        <v>0.8445988877669394</v>
+      </c>
+      <c r="U17">
+        <v>0.09773027832878751</v>
+      </c>
+      <c r="V17">
+        <v>0.2686</v>
+      </c>
+      <c r="W17">
+        <v>0.0714799255696752</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>1.521287057940796</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09216631998343239</v>
+      </c>
+      <c r="C18">
+        <v>3068.315958044258</v>
+      </c>
+      <c r="D18">
+        <v>3755.627958044258</v>
+      </c>
+      <c r="E18">
+        <v>687.312</v>
+      </c>
+      <c r="F18">
+        <v>687.312</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>4295.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>398.5</v>
+      </c>
+      <c r="K18">
+        <v>302.7</v>
+      </c>
+      <c r="L18">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M18">
+        <v>112.1213978587156</v>
+      </c>
+      <c r="N18">
+        <v>-16.3213978587156</v>
+      </c>
+      <c r="O18">
+        <v>-4.38392746485101</v>
+      </c>
+      <c r="P18">
+        <v>-11.93747039386459</v>
+      </c>
+      <c r="Q18">
+        <v>290.7625296061354</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08578050445077273</v>
+      </c>
+      <c r="T18">
+        <v>0.8578328156370185</v>
+      </c>
+      <c r="U18">
+        <v>0.1631302783287875</v>
+      </c>
+      <c r="V18">
+        <v>0.2295001711664779</v>
+      </c>
+      <c r="W18">
+        <v>0.1256918515298956</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.8544310170010347</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09340962276672025</v>
+      </c>
+      <c r="C19">
+        <v>2978.599214394324</v>
+      </c>
+      <c r="D19">
+        <v>3708.868214394324</v>
+      </c>
+      <c r="E19">
+        <v>730.269</v>
+      </c>
+      <c r="F19">
+        <v>730.269</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>4295.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>398.5</v>
+      </c>
+      <c r="K19">
+        <v>302.7</v>
+      </c>
+      <c r="L19">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M19">
+        <v>119.1289852248853</v>
+      </c>
+      <c r="N19">
+        <v>-23.32898522488532</v>
+      </c>
+      <c r="O19">
+        <v>-6.266165431404196</v>
+      </c>
+      <c r="P19">
+        <v>-17.06281979348112</v>
+      </c>
+      <c r="Q19">
+        <v>285.6371802065188</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.08634653462487843</v>
+      </c>
+      <c r="T19">
+        <v>0.8681681507651754</v>
+      </c>
+      <c r="U19">
+        <v>0.1631302783287875</v>
+      </c>
+      <c r="V19">
+        <v>0.2160001610978616</v>
+      </c>
+      <c r="W19">
+        <v>0.1278941119298304</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.8041703689421503</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.10441360629085</v>
+      </c>
+      <c r="C20">
+        <v>2567.50929937703</v>
+      </c>
+      <c r="D20">
+        <v>3340.735299377031</v>
+      </c>
+      <c r="E20">
+        <v>773.2259999999999</v>
+      </c>
+      <c r="F20">
+        <v>773.2259999999999</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>4295.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>398.5</v>
+      </c>
+      <c r="K20">
+        <v>302.7</v>
+      </c>
+      <c r="L20">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M20">
+        <v>166.4989697910551</v>
+      </c>
+      <c r="N20">
+        <v>-70.69896979105505</v>
+      </c>
+      <c r="O20">
+        <v>-18.98974328587739</v>
+      </c>
+      <c r="P20">
+        <v>-51.70922650517766</v>
+      </c>
+      <c r="Q20">
+        <v>250.9907734948223</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.08737110302376941</v>
+      </c>
+      <c r="T20">
+        <v>0.8868760894028775</v>
+      </c>
+      <c r="U20">
+        <v>0.2153302783287875</v>
+      </c>
+      <c r="V20">
+        <v>0.1545467820749388</v>
+      </c>
+      <c r="W20">
+        <v>0.1820516767297725</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.5753789354986552</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1061789090741378</v>
+      </c>
+      <c r="C21">
+        <v>2472.190606861658</v>
+      </c>
+      <c r="D21">
+        <v>3288.373606861658</v>
+      </c>
+      <c r="E21">
+        <v>816.183</v>
+      </c>
+      <c r="F21">
+        <v>816.183</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>4295.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>398.5</v>
+      </c>
+      <c r="K21">
+        <v>302.7</v>
+      </c>
+      <c r="L21">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M21">
+        <v>175.7489125572248</v>
+      </c>
+      <c r="N21">
+        <v>-79.94891255722479</v>
+      </c>
+      <c r="O21">
+        <v>-21.47427791287058</v>
+      </c>
+      <c r="P21">
+        <v>-58.47463464435421</v>
+      </c>
+      <c r="Q21">
+        <v>244.2253653556458</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.08797074627097642</v>
+      </c>
+      <c r="T21">
+        <v>0.8978251769263699</v>
+      </c>
+      <c r="U21">
+        <v>0.2153302783287875</v>
+      </c>
+      <c r="V21">
+        <v>0.1464127409130999</v>
+      </c>
+      <c r="W21">
+        <v>0.1838031820770891</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.5450958336303049</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1079442118574257</v>
+      </c>
+      <c r="C22">
+        <v>2378.487987715025</v>
+      </c>
+      <c r="D22">
+        <v>3237.627987715025</v>
+      </c>
+      <c r="E22">
+        <v>859.14</v>
+      </c>
+      <c r="F22">
+        <v>859.14</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>4295.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>398.5</v>
+      </c>
+      <c r="K22">
+        <v>302.7</v>
+      </c>
+      <c r="L22">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M22">
+        <v>184.9988553233945</v>
+      </c>
+      <c r="N22">
+        <v>-89.19885532339453</v>
+      </c>
+      <c r="O22">
+        <v>-23.95881253986377</v>
+      </c>
+      <c r="P22">
+        <v>-65.24004278353075</v>
+      </c>
+      <c r="Q22">
+        <v>237.4599572164692</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.08858538059936363</v>
+      </c>
+      <c r="T22">
+        <v>0.9090479916379495</v>
+      </c>
+      <c r="U22">
+        <v>0.2153302783287875</v>
+      </c>
+      <c r="V22">
+        <v>0.1390921038674449</v>
+      </c>
+      <c r="W22">
+        <v>0.185379536889674</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.5178410419487895</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1161488774864006</v>
+      </c>
+      <c r="C23">
+        <v>2118.858667196745</v>
+      </c>
+      <c r="D23">
+        <v>3020.955667196745</v>
+      </c>
+      <c r="E23">
+        <v>902.097</v>
+      </c>
+      <c r="F23">
+        <v>902.097</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>4295.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>398.5</v>
+      </c>
+      <c r="K23">
+        <v>302.7</v>
+      </c>
+      <c r="L23">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M23">
+        <v>221.3117080895642</v>
+      </c>
+      <c r="N23">
+        <v>-125.5117080895642</v>
+      </c>
+      <c r="O23">
+        <v>-33.71244479285695</v>
+      </c>
+      <c r="P23">
+        <v>-91.79926329670727</v>
+      </c>
+      <c r="Q23">
+        <v>210.9007367032927</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.08939198395592138</v>
+      </c>
+      <c r="T23">
+        <v>0.9237760333341217</v>
+      </c>
+      <c r="U23">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V23">
+        <v>0.1162698540539319</v>
+      </c>
+      <c r="W23">
+        <v>0.2168057626724889</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.43287361896475</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1182141802696884</v>
+      </c>
+      <c r="C24">
+        <v>2025.853467719603</v>
+      </c>
+      <c r="D24">
+        <v>2970.907467719603</v>
+      </c>
+      <c r="E24">
+        <v>945.054</v>
+      </c>
+      <c r="F24">
+        <v>945.054</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>4295.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>398.5</v>
+      </c>
+      <c r="K24">
+        <v>302.7</v>
+      </c>
+      <c r="L24">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M24">
+        <v>231.850360855734</v>
+      </c>
+      <c r="N24">
+        <v>-136.0503608557339</v>
+      </c>
+      <c r="O24">
+        <v>-36.54312692585014</v>
+      </c>
+      <c r="P24">
+        <v>-99.5072339298838</v>
+      </c>
+      <c r="Q24">
+        <v>203.1927660701162</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09004059913484344</v>
+      </c>
+      <c r="T24">
+        <v>0.9356193158127644</v>
+      </c>
+      <c r="U24">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V24">
+        <v>0.1109848606878441</v>
+      </c>
+      <c r="W24">
+        <v>0.218102331565957</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.4131975453754432</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1202794830529763</v>
+      </c>
+      <c r="C25">
+        <v>1934.479540868384</v>
+      </c>
+      <c r="D25">
+        <v>2922.490540868384</v>
+      </c>
+      <c r="E25">
+        <v>988.011</v>
+      </c>
+      <c r="F25">
+        <v>988.011</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>4295.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>398.5</v>
+      </c>
+      <c r="K25">
+        <v>302.7</v>
+      </c>
+      <c r="L25">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M25">
+        <v>242.3890136219037</v>
+      </c>
+      <c r="N25">
+        <v>-146.5890136219037</v>
+      </c>
+      <c r="O25">
+        <v>-39.37380905884332</v>
+      </c>
+      <c r="P25">
+        <v>-107.2152045630603</v>
+      </c>
+      <c r="Q25">
+        <v>195.4847954369396</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09070606146126997</v>
+      </c>
+      <c r="T25">
+        <v>0.9477702160181249</v>
+      </c>
+      <c r="U25">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V25">
+        <v>0.1061594319622856</v>
+      </c>
+      <c r="W25">
+        <v>0.219286155338254</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.3952324347069457</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1223447858362642</v>
+      </c>
+      <c r="C26">
+        <v>1844.658410934205</v>
+      </c>
+      <c r="D26">
+        <v>2875.626410934205</v>
+      </c>
+      <c r="E26">
+        <v>1030.968</v>
+      </c>
+      <c r="F26">
+        <v>1030.968</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>4295.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>398.5</v>
+      </c>
+      <c r="K26">
+        <v>302.7</v>
+      </c>
+      <c r="L26">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M26">
+        <v>252.9276663880734</v>
+      </c>
+      <c r="N26">
+        <v>-157.1276663880734</v>
+      </c>
+      <c r="O26">
+        <v>-42.2044911918365</v>
+      </c>
+      <c r="P26">
+        <v>-114.9231751962369</v>
+      </c>
+      <c r="Q26">
+        <v>187.7768248037631</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09138903595418142</v>
+      </c>
+      <c r="T26">
+        <v>0.9602408767552055</v>
+      </c>
+      <c r="U26">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V26">
+        <v>0.1017361222971904</v>
+      </c>
+      <c r="W26">
+        <v>0.2203713271295262</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.3787644165941564</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1244100886195521</v>
+      </c>
+      <c r="C27">
+        <v>1756.316556410324</v>
+      </c>
+      <c r="D27">
+        <v>2830.241556410324</v>
+      </c>
+      <c r="E27">
+        <v>1073.925</v>
+      </c>
+      <c r="F27">
+        <v>1073.925</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>4295.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>398.5</v>
+      </c>
+      <c r="K27">
+        <v>302.7</v>
+      </c>
+      <c r="L27">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M27">
+        <v>263.4663191542431</v>
+      </c>
+      <c r="N27">
+        <v>-167.6663191542431</v>
+      </c>
+      <c r="O27">
+        <v>-45.03517332482971</v>
+      </c>
+      <c r="P27">
+        <v>-122.6311458294134</v>
+      </c>
+      <c r="Q27">
+        <v>180.0688541705866</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09209022310023718</v>
+      </c>
+      <c r="T27">
+        <v>0.9730440884452749</v>
+      </c>
+      <c r="U27">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V27">
+        <v>0.09766667740530276</v>
+      </c>
+      <c r="W27">
+        <v>0.2213696851774967</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.36361383993039</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1264753914028399</v>
+      </c>
+      <c r="C28">
+        <v>1669.385025115602</v>
+      </c>
+      <c r="D28">
+        <v>2786.267025115602</v>
+      </c>
+      <c r="E28">
+        <v>1116.882</v>
+      </c>
+      <c r="F28">
+        <v>1116.882</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>4295.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>398.5</v>
+      </c>
+      <c r="K28">
+        <v>302.7</v>
+      </c>
+      <c r="L28">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M28">
+        <v>274.0049719204129</v>
+      </c>
+      <c r="N28">
+        <v>-178.2049719204128</v>
+      </c>
+      <c r="O28">
+        <v>-47.86585545782289</v>
+      </c>
+      <c r="P28">
+        <v>-130.33911646259</v>
+      </c>
+      <c r="Q28">
+        <v>172.36088353741</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09281036125024039</v>
+      </c>
+      <c r="T28">
+        <v>0.9861933328837248</v>
+      </c>
+      <c r="U28">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V28">
+        <v>0.09391026673586804</v>
+      </c>
+      <c r="W28">
+        <v>0.2222912464525463</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.3496286922407597</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1285406941861278</v>
+      </c>
+      <c r="C29">
+        <v>1583.799084648836</v>
+      </c>
+      <c r="D29">
+        <v>2743.638084648836</v>
+      </c>
+      <c r="E29">
+        <v>1159.839</v>
+      </c>
+      <c r="F29">
+        <v>1159.839</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>4295.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>398.5</v>
+      </c>
+      <c r="K29">
+        <v>302.7</v>
+      </c>
+      <c r="L29">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M29">
+        <v>284.5436246865826</v>
+      </c>
+      <c r="N29">
+        <v>-188.7436246865826</v>
+      </c>
+      <c r="O29">
+        <v>-50.69653759081608</v>
+      </c>
+      <c r="P29">
+        <v>-138.0470870957665</v>
+      </c>
+      <c r="Q29">
+        <v>164.6529129042335</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09355022921257244</v>
+      </c>
+      <c r="T29">
+        <v>0.9997028305944607</v>
+      </c>
+      <c r="U29">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V29">
+        <v>0.09043210870861366</v>
+      </c>
+      <c r="W29">
+        <v>0.2231445439294442</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.3366794814170277</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1306059969694157</v>
+      </c>
+      <c r="C30">
+        <v>1499.497904447155</v>
+      </c>
+      <c r="D30">
+        <v>2702.293904447155</v>
+      </c>
+      <c r="E30">
+        <v>1202.796</v>
+      </c>
+      <c r="F30">
+        <v>1202.796</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>4295.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>398.5</v>
+      </c>
+      <c r="K30">
+        <v>302.7</v>
+      </c>
+      <c r="L30">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M30">
+        <v>295.0822774527523</v>
+      </c>
+      <c r="N30">
+        <v>-199.2822774527523</v>
+      </c>
+      <c r="O30">
+        <v>-53.52721972380927</v>
+      </c>
+      <c r="P30">
+        <v>-145.755057728943</v>
+      </c>
+      <c r="Q30">
+        <v>156.944942271057</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09431064906274707</v>
+      </c>
+      <c r="T30">
+        <v>1.013587592130495</v>
+      </c>
+      <c r="U30">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V30">
+        <v>0.0872023905404489</v>
+      </c>
+      <c r="W30">
+        <v>0.2239368915865636</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.3246552142235626</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1326712997527035</v>
+      </c>
+      <c r="C31">
+        <v>1416.424266164231</v>
+      </c>
+      <c r="D31">
+        <v>2662.177266164231</v>
+      </c>
+      <c r="E31">
+        <v>1245.753</v>
+      </c>
+      <c r="F31">
+        <v>1245.753</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>4295.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>398.5</v>
+      </c>
+      <c r="K31">
+        <v>302.7</v>
+      </c>
+      <c r="L31">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M31">
+        <v>305.620930218922</v>
+      </c>
+      <c r="N31">
+        <v>-209.820930218922</v>
+      </c>
+      <c r="O31">
+        <v>-56.35790185680245</v>
+      </c>
+      <c r="P31">
+        <v>-153.4630283621196</v>
+      </c>
+      <c r="Q31">
+        <v>149.2369716378804</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.0950924891903914</v>
+      </c>
+      <c r="T31">
+        <v>1.027863473709798</v>
+      </c>
+      <c r="U31">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V31">
+        <v>0.08419541155629549</v>
+      </c>
+      <c r="W31">
+        <v>0.2246745945776747</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.3134602068365432</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1347366025359914</v>
+      </c>
+      <c r="C32">
+        <v>1334.524299468436</v>
+      </c>
+      <c r="D32">
+        <v>2623.234299468436</v>
+      </c>
+      <c r="E32">
+        <v>1288.71</v>
+      </c>
+      <c r="F32">
+        <v>1288.71</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>4295.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>398.5</v>
+      </c>
+      <c r="K32">
+        <v>302.7</v>
+      </c>
+      <c r="L32">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M32">
+        <v>316.1595829850917</v>
+      </c>
+      <c r="N32">
+        <v>-220.3595829850917</v>
+      </c>
+      <c r="O32">
+        <v>-59.18858398979564</v>
+      </c>
+      <c r="P32">
+        <v>-161.1709989952961</v>
+      </c>
+      <c r="Q32">
+        <v>141.5290010047039</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09589666760739697</v>
+      </c>
+      <c r="T32">
+        <v>1.042547237619937</v>
+      </c>
+      <c r="U32">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V32">
+        <v>0.08138889783775231</v>
+      </c>
+      <c r="W32">
+        <v>0.2253631173693785</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.303011533275325</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1368019053192793</v>
+      </c>
+      <c r="C33">
+        <v>1253.747240695524</v>
+      </c>
+      <c r="D33">
+        <v>2585.414240695524</v>
+      </c>
+      <c r="E33">
+        <v>1331.667</v>
+      </c>
+      <c r="F33">
+        <v>1331.667</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>4295.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>398.5</v>
+      </c>
+      <c r="K33">
+        <v>302.7</v>
+      </c>
+      <c r="L33">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M33">
+        <v>326.6982357512614</v>
+      </c>
+      <c r="N33">
+        <v>-230.8982357512614</v>
+      </c>
+      <c r="O33">
+        <v>-62.01926612278882</v>
+      </c>
+      <c r="P33">
+        <v>-168.8789696284726</v>
+      </c>
+      <c r="Q33">
+        <v>133.8210303715274</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09672415554373608</v>
+      </c>
+      <c r="T33">
+        <v>1.057656617875299</v>
+      </c>
+      <c r="U33">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V33">
+        <v>0.07876344952040545</v>
+      </c>
+      <c r="W33">
+        <v>0.226007219335811</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.2932369676857984</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1388672081025672</v>
+      </c>
+      <c r="C34">
+        <v>1174.04521208211</v>
+      </c>
+      <c r="D34">
+        <v>2548.66921208211</v>
+      </c>
+      <c r="E34">
+        <v>1374.624</v>
+      </c>
+      <c r="F34">
+        <v>1374.624</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>4295.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>398.5</v>
+      </c>
+      <c r="K34">
+        <v>302.7</v>
+      </c>
+      <c r="L34">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M34">
+        <v>337.2368885174312</v>
+      </c>
+      <c r="N34">
+        <v>-241.4368885174312</v>
+      </c>
+      <c r="O34">
+        <v>-64.84994825578202</v>
+      </c>
+      <c r="P34">
+        <v>-176.5869402616492</v>
+      </c>
+      <c r="Q34">
+        <v>126.1130597383508</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.0975759813605557</v>
+      </c>
+      <c r="T34">
+        <v>1.073210391667583</v>
+      </c>
+      <c r="U34">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V34">
+        <v>0.07630209172289278</v>
+      </c>
+      <c r="W34">
+        <v>0.2266110649293415</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.2840733124456172</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1409325108858551</v>
+      </c>
+      <c r="C35">
+        <v>1095.373019561114</v>
+      </c>
+      <c r="D35">
+        <v>2512.954019561113</v>
+      </c>
+      <c r="E35">
+        <v>1417.581</v>
+      </c>
+      <c r="F35">
+        <v>1417.581</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>4295.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>398.5</v>
+      </c>
+      <c r="K35">
+        <v>302.7</v>
+      </c>
+      <c r="L35">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M35">
+        <v>347.7755412836009</v>
+      </c>
+      <c r="N35">
+        <v>-251.9755412836009</v>
+      </c>
+      <c r="O35">
+        <v>-67.6806303887752</v>
+      </c>
+      <c r="P35">
+        <v>-184.2949108948257</v>
+      </c>
+      <c r="Q35">
+        <v>118.4050891051743</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.09845323481369833</v>
+      </c>
+      <c r="T35">
+        <v>1.08922845721486</v>
+      </c>
+      <c r="U35">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V35">
+        <v>0.07398990712522938</v>
+      </c>
+      <c r="W35">
+        <v>0.2271783138202338</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.2754650302502955</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1429978136691429</v>
+      </c>
+      <c r="C36">
+        <v>1017.687967323536</v>
+      </c>
+      <c r="D36">
+        <v>2478.225967323536</v>
+      </c>
+      <c r="E36">
+        <v>1460.538</v>
+      </c>
+      <c r="F36">
+        <v>1460.538</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>4295.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>398.5</v>
+      </c>
+      <c r="K36">
+        <v>302.7</v>
+      </c>
+      <c r="L36">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M36">
+        <v>358.3141940497707</v>
+      </c>
+      <c r="N36">
+        <v>-262.5141940497707</v>
+      </c>
+      <c r="O36">
+        <v>-70.5113125217684</v>
+      </c>
+      <c r="P36">
+        <v>-192.0028815280023</v>
+      </c>
+      <c r="Q36">
+        <v>110.6971184719977</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.09935707170481498</v>
+      </c>
+      <c r="T36">
+        <v>1.105731918687813</v>
+      </c>
+      <c r="U36">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V36">
+        <v>0.07181373338625202</v>
+      </c>
+      <c r="W36">
+        <v>0.227712195129309</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.2673631175958751</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1450631164524308</v>
+      </c>
+      <c r="C37">
+        <v>940.9496875467505</v>
+      </c>
+      <c r="D37">
+        <v>2444.444687546751</v>
+      </c>
+      <c r="E37">
+        <v>1503.495</v>
+      </c>
+      <c r="F37">
+        <v>1503.495</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>4295.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>398.5</v>
+      </c>
+      <c r="K37">
+        <v>302.7</v>
+      </c>
+      <c r="L37">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M37">
+        <v>368.8528468159404</v>
+      </c>
+      <c r="N37">
+        <v>-273.0528468159404</v>
+      </c>
+      <c r="O37">
+        <v>-73.34199465476158</v>
+      </c>
+      <c r="P37">
+        <v>-199.7108521611788</v>
+      </c>
+      <c r="Q37">
+        <v>102.9891478388212</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1002887189618121</v>
+      </c>
+      <c r="T37">
+        <v>1.122743178975318</v>
+      </c>
+      <c r="U37">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V37">
+        <v>0.06976191243235912</v>
+      </c>
+      <c r="W37">
+        <v>0.2282155689350084</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.2597241713788501</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1471284192357187</v>
+      </c>
+      <c r="C38">
+        <v>865.1199838615944</v>
+      </c>
+      <c r="D38">
+        <v>2411.571983861594</v>
+      </c>
+      <c r="E38">
+        <v>1546.452</v>
+      </c>
+      <c r="F38">
+        <v>1546.452</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>4295.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>398.5</v>
+      </c>
+      <c r="K38">
+        <v>302.7</v>
+      </c>
+      <c r="L38">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M38">
+        <v>379.39149958211</v>
+      </c>
+      <c r="N38">
+        <v>-283.59149958211</v>
+      </c>
+      <c r="O38">
+        <v>-76.17267678775475</v>
+      </c>
+      <c r="P38">
+        <v>-207.4188227943553</v>
+      </c>
+      <c r="Q38">
+        <v>95.28117720564472</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1012494801955904</v>
+      </c>
+      <c r="T38">
+        <v>1.140286041146807</v>
+      </c>
+      <c r="U38">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V38">
+        <v>0.06782408153146026</v>
+      </c>
+      <c r="W38">
+        <v>0.22869097752928</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.2525096110627709</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1491937220190065</v>
+      </c>
+      <c r="C39">
+        <v>790.1626872821219</v>
+      </c>
+      <c r="D39">
+        <v>2379.571687282122</v>
+      </c>
+      <c r="E39">
+        <v>1589.409</v>
+      </c>
+      <c r="F39">
+        <v>1589.409</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>4295.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>398.5</v>
+      </c>
+      <c r="K39">
+        <v>302.7</v>
+      </c>
+      <c r="L39">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M39">
+        <v>389.9301523482798</v>
+      </c>
+      <c r="N39">
+        <v>-294.1301523482798</v>
+      </c>
+      <c r="O39">
+        <v>-79.00335892074796</v>
+      </c>
+      <c r="P39">
+        <v>-215.1267934275319</v>
+      </c>
+      <c r="Q39">
+        <v>87.57320657246814</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1022407417859966</v>
+      </c>
+      <c r="T39">
+        <v>1.158385819577708</v>
+      </c>
+      <c r="U39">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V39">
+        <v>0.06599099824682619</v>
+      </c>
+      <c r="W39">
+        <v>0.2291406883616991</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.2456850269799933</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1512590248022944</v>
+      </c>
+      <c r="C40">
+        <v>716.0435234555625</v>
+      </c>
+      <c r="D40">
+        <v>2348.409523455563</v>
+      </c>
+      <c r="E40">
+        <v>1632.366</v>
+      </c>
+      <c r="F40">
+        <v>1632.366</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>4295.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>398.5</v>
+      </c>
+      <c r="K40">
+        <v>302.7</v>
+      </c>
+      <c r="L40">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M40">
+        <v>400.4688051144495</v>
+      </c>
+      <c r="N40">
+        <v>-304.6688051144495</v>
+      </c>
+      <c r="O40">
+        <v>-81.83404105374115</v>
+      </c>
+      <c r="P40">
+        <v>-222.8347640607084</v>
+      </c>
+      <c r="Q40">
+        <v>79.86523593929161</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1032639795567385</v>
+      </c>
+      <c r="T40">
+        <v>1.177069461828962</v>
+      </c>
+      <c r="U40">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V40">
+        <v>0.06425439302980446</v>
+      </c>
+      <c r="W40">
+        <v>0.2295667302029383</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.2392196315331513</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1533243275855823</v>
+      </c>
+      <c r="C41">
+        <v>642.7299902081779</v>
+      </c>
+      <c r="D41">
+        <v>2318.052990208178</v>
+      </c>
+      <c r="E41">
+        <v>1675.323</v>
+      </c>
+      <c r="F41">
+        <v>1675.323</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>4295.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>398.5</v>
+      </c>
+      <c r="K41">
+        <v>302.7</v>
+      </c>
+      <c r="L41">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M41">
+        <v>411.0074578806193</v>
+      </c>
+      <c r="N41">
+        <v>-315.2074578806193</v>
+      </c>
+      <c r="O41">
+        <v>-84.66472318673435</v>
+      </c>
+      <c r="P41">
+        <v>-230.5427346938849</v>
+      </c>
+      <c r="Q41">
+        <v>72.15726530611505</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.104320766106849</v>
+      </c>
+      <c r="T41">
+        <v>1.196365682514682</v>
+      </c>
+      <c r="U41">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V41">
+        <v>0.06260684449057868</v>
+      </c>
+      <c r="W41">
+        <v>0.2299709237446267</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.2330857948271731</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1553896303688702</v>
+      </c>
+      <c r="C42">
+        <v>570.1912444672855</v>
+      </c>
+      <c r="D42">
+        <v>2288.471244467285</v>
+      </c>
+      <c r="E42">
+        <v>1718.28</v>
+      </c>
+      <c r="F42">
+        <v>1718.28</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>4295.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>398.5</v>
+      </c>
+      <c r="K42">
+        <v>302.7</v>
+      </c>
+      <c r="L42">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M42">
+        <v>421.546110646789</v>
+      </c>
+      <c r="N42">
+        <v>-325.746110646789</v>
+      </c>
+      <c r="O42">
+        <v>-87.49540531972752</v>
+      </c>
+      <c r="P42">
+        <v>-238.2507053270614</v>
+      </c>
+      <c r="Q42">
+        <v>64.44929467293855</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1054127788752965</v>
+      </c>
+      <c r="T42">
+        <v>1.216305110556594</v>
+      </c>
+      <c r="U42">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V42">
+        <v>0.06104167337831423</v>
+      </c>
+      <c r="W42">
+        <v>0.2303549076092307</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.2272586499564938</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1574549331521581</v>
+      </c>
+      <c r="C43">
+        <v>498.3979977324166</v>
+      </c>
+      <c r="D43">
+        <v>2259.634997732417</v>
+      </c>
+      <c r="E43">
+        <v>1761.237</v>
+      </c>
+      <c r="F43">
+        <v>1761.237</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>4295.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>398.5</v>
+      </c>
+      <c r="K43">
+        <v>302.7</v>
+      </c>
+      <c r="L43">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M43">
+        <v>432.0847634129588</v>
+      </c>
+      <c r="N43">
+        <v>-336.2847634129587</v>
+      </c>
+      <c r="O43">
+        <v>-90.32608745272071</v>
+      </c>
+      <c r="P43">
+        <v>-245.958675960238</v>
+      </c>
+      <c r="Q43">
+        <v>56.74132403976196</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1065418090257252</v>
+      </c>
+      <c r="T43">
+        <v>1.236920451413485</v>
+      </c>
+      <c r="U43">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V43">
+        <v>0.05955285207640412</v>
+      </c>
+      <c r="W43">
+        <v>0.2307201605536102</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.2217157560551158</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.159520235935446</v>
+      </c>
+      <c r="C44">
+        <v>427.3224193509377</v>
+      </c>
+      <c r="D44">
+        <v>2231.516419350938</v>
+      </c>
+      <c r="E44">
+        <v>1804.194</v>
+      </c>
+      <c r="F44">
+        <v>1804.194</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>4295.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>398.5</v>
+      </c>
+      <c r="K44">
+        <v>302.7</v>
+      </c>
+      <c r="L44">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M44">
+        <v>442.6234161791285</v>
+      </c>
+      <c r="N44">
+        <v>-346.8234161791285</v>
+      </c>
+      <c r="O44">
+        <v>-93.1567695857139</v>
+      </c>
+      <c r="P44">
+        <v>-253.6666465934146</v>
+      </c>
+      <c r="Q44">
+        <v>49.03335340658543</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1077097712503067</v>
+      </c>
+      <c r="T44">
+        <v>1.258246666093028</v>
+      </c>
+      <c r="U44">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V44">
+        <v>0.05813492702696593</v>
+      </c>
+      <c r="W44">
+        <v>0.2310680205006382</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.216436809482375</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1615855387187338</v>
+      </c>
+      <c r="C45">
+        <v>356.938046926648</v>
+      </c>
+      <c r="D45">
+        <v>2204.089046926648</v>
+      </c>
+      <c r="E45">
+        <v>1847.151</v>
+      </c>
+      <c r="F45">
+        <v>1847.151</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>4295.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>398.5</v>
+      </c>
+      <c r="K45">
+        <v>302.7</v>
+      </c>
+      <c r="L45">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M45">
+        <v>453.1620689452981</v>
+      </c>
+      <c r="N45">
+        <v>-357.3620689452981</v>
+      </c>
+      <c r="O45">
+        <v>-95.98745171870708</v>
+      </c>
+      <c r="P45">
+        <v>-261.3746172265911</v>
+      </c>
+      <c r="Q45">
+        <v>41.32538277340893</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1089187146055752</v>
+      </c>
+      <c r="T45">
+        <v>1.280321169006941</v>
+      </c>
+      <c r="U45">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V45">
+        <v>0.0567829519798272</v>
+      </c>
+      <c r="W45">
+        <v>0.2313997009152463</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.2114033953083663</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1636508415020217</v>
+      </c>
+      <c r="C46">
+        <v>287.2197032551228</v>
+      </c>
+      <c r="D46">
+        <v>2177.327703255123</v>
+      </c>
+      <c r="E46">
+        <v>1890.108</v>
+      </c>
+      <c r="F46">
+        <v>1890.108</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>4295.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>398.5</v>
+      </c>
+      <c r="K46">
+        <v>302.7</v>
+      </c>
+      <c r="L46">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M46">
+        <v>463.7007217114679</v>
+      </c>
+      <c r="N46">
+        <v>-367.9007217114679</v>
+      </c>
+      <c r="O46">
+        <v>-98.81813385170028</v>
+      </c>
+      <c r="P46">
+        <v>-269.0825878597676</v>
+      </c>
+      <c r="Q46">
+        <v>33.61741214023237</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1101708345092462</v>
+      </c>
+      <c r="T46">
+        <v>1.303184047024922</v>
+      </c>
+      <c r="U46">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V46">
+        <v>0.05549243034392203</v>
+      </c>
+      <c r="W46">
+        <v>0.2317163049473723</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.2065987726877216</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1657161442853096</v>
+      </c>
+      <c r="C47">
+        <v>218.143419237731</v>
+      </c>
+      <c r="D47">
+        <v>2151.208419237731</v>
+      </c>
+      <c r="E47">
+        <v>1933.065</v>
+      </c>
+      <c r="F47">
+        <v>1933.065</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>4295.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>398.5</v>
+      </c>
+      <c r="K47">
+        <v>302.7</v>
+      </c>
+      <c r="L47">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M47">
+        <v>474.2393744776376</v>
+      </c>
+      <c r="N47">
+        <v>-378.4393744776376</v>
+      </c>
+      <c r="O47">
+        <v>-101.6488159846935</v>
+      </c>
+      <c r="P47">
+        <v>-276.7905584929441</v>
+      </c>
+      <c r="Q47">
+        <v>25.90944150705587</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.111468486045778</v>
+      </c>
+      <c r="T47">
+        <v>1.326878302425375</v>
+      </c>
+      <c r="U47">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V47">
+        <v>0.0542592652251682</v>
+      </c>
+      <c r="W47">
+        <v>0.2320188376891815</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.2020076888502167</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1677814470685974</v>
+      </c>
+      <c r="C48">
+        <v>149.6863622782371</v>
+      </c>
+      <c r="D48">
+        <v>2125.708362278237</v>
+      </c>
+      <c r="E48">
+        <v>1976.022</v>
+      </c>
+      <c r="F48">
+        <v>1976.022</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>4295.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>398.5</v>
+      </c>
+      <c r="K48">
+        <v>302.7</v>
+      </c>
+      <c r="L48">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M48">
+        <v>484.7780272438073</v>
+      </c>
+      <c r="N48">
+        <v>-388.9780272438073</v>
+      </c>
+      <c r="O48">
+        <v>-104.4794981176866</v>
+      </c>
+      <c r="P48">
+        <v>-284.4985291261207</v>
+      </c>
+      <c r="Q48">
+        <v>18.20147087387932</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1128141987503294</v>
+      </c>
+      <c r="T48">
+        <v>1.35145012284066</v>
+      </c>
+      <c r="U48">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V48">
+        <v>0.05307971598114281</v>
+      </c>
+      <c r="W48">
+        <v>0.2323082168335208</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1976162173534728</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1698467498518853</v>
+      </c>
+      <c r="C49">
+        <v>81.82676971238857</v>
+      </c>
+      <c r="D49">
+        <v>2100.805769712389</v>
+      </c>
+      <c r="E49">
+        <v>2018.979</v>
+      </c>
+      <c r="F49">
+        <v>2018.979</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>4295.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>398.5</v>
+      </c>
+      <c r="K49">
+        <v>302.7</v>
+      </c>
+      <c r="L49">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M49">
+        <v>495.3166800099771</v>
+      </c>
+      <c r="N49">
+        <v>-399.5166800099771</v>
+      </c>
+      <c r="O49">
+        <v>-107.3101802506798</v>
+      </c>
+      <c r="P49">
+        <v>-292.2064997592972</v>
+      </c>
+      <c r="Q49">
+        <v>10.49350024070276</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1142106930663734</v>
+      </c>
+      <c r="T49">
+        <v>1.376949181762182</v>
+      </c>
+      <c r="U49">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V49">
+        <v>0.05195036032196956</v>
+      </c>
+      <c r="W49">
+        <v>0.2325852819717179</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.19341161698425</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1719120526351732</v>
+      </c>
+      <c r="C50">
+        <v>14.54388686254379</v>
+      </c>
+      <c r="D50">
+        <v>2076.479886862543</v>
+      </c>
+      <c r="E50">
+        <v>2061.936</v>
+      </c>
+      <c r="F50">
+        <v>2061.936</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>4295.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>398.5</v>
+      </c>
+      <c r="K50">
+        <v>302.7</v>
+      </c>
+      <c r="L50">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M50">
+        <v>505.8553327761467</v>
+      </c>
+      <c r="N50">
+        <v>-410.0553327761467</v>
+      </c>
+      <c r="O50">
+        <v>-110.140862383673</v>
+      </c>
+      <c r="P50">
+        <v>-299.9144703924737</v>
+      </c>
+      <c r="Q50">
+        <v>2.785529607526257</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1156608987022652</v>
+      </c>
+      <c r="T50">
+        <v>1.403428973719147</v>
+      </c>
+      <c r="U50">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V50">
+        <v>0.0508680611485952</v>
+      </c>
+      <c r="W50">
+        <v>0.2328508027291569</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.1893822082970782</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.173977355418461</v>
+      </c>
+      <c r="C51">
+        <v>-52.18209065326118</v>
+      </c>
+      <c r="D51">
+        <v>2052.710909346739</v>
+      </c>
+      <c r="E51">
+        <v>2104.893</v>
+      </c>
+      <c r="F51">
+        <v>2104.893</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>4295.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>398.5</v>
+      </c>
+      <c r="K51">
+        <v>302.7</v>
+      </c>
+      <c r="L51">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M51">
+        <v>516.3939855423165</v>
+      </c>
+      <c r="N51">
+        <v>-420.5939855423165</v>
+      </c>
+      <c r="O51">
+        <v>-112.9715445166662</v>
+      </c>
+      <c r="P51">
+        <v>-307.6224410256503</v>
+      </c>
+      <c r="Q51">
+        <v>-4.922441025650301</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1171679751474076</v>
+      </c>
+      <c r="T51">
+        <v>1.43094718889011</v>
+      </c>
+      <c r="U51">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V51">
+        <v>0.04982993745168508</v>
+      </c>
+      <c r="W51">
+        <v>0.2331054859046595</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1855172652706072</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1760426582017489</v>
+      </c>
+      <c r="C52">
+        <v>-118.3700706948352</v>
+      </c>
+      <c r="D52">
+        <v>2029.479929305165</v>
+      </c>
+      <c r="E52">
+        <v>2147.85</v>
+      </c>
+      <c r="F52">
+        <v>2147.85</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>4295.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>398.5</v>
+      </c>
+      <c r="K52">
+        <v>302.7</v>
+      </c>
+      <c r="L52">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M52">
+        <v>526.9326383084863</v>
+      </c>
+      <c r="N52">
+        <v>-431.1326383084863</v>
+      </c>
+      <c r="O52">
+        <v>-115.8022266496594</v>
+      </c>
+      <c r="P52">
+        <v>-315.3304116588268</v>
+      </c>
+      <c r="Q52">
+        <v>-12.63041165882686</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1187353346503558</v>
+      </c>
+      <c r="T52">
+        <v>1.459566132667913</v>
+      </c>
+      <c r="U52">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V52">
+        <v>0.04883333870265138</v>
+      </c>
+      <c r="W52">
+        <v>0.2333499817531421</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.181806919965195</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1781079609850368</v>
+      </c>
+      <c r="C53">
+        <v>-184.0381147628145</v>
+      </c>
+      <c r="D53">
+        <v>2006.768885237185</v>
+      </c>
+      <c r="E53">
+        <v>2190.807</v>
+      </c>
+      <c r="F53">
+        <v>2190.807</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>4295.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>398.5</v>
+      </c>
+      <c r="K53">
+        <v>302.7</v>
+      </c>
+      <c r="L53">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M53">
+        <v>537.4712910746559</v>
+      </c>
+      <c r="N53">
+        <v>-441.6712910746559</v>
+      </c>
+      <c r="O53">
+        <v>-118.6329087826526</v>
+      </c>
+      <c r="P53">
+        <v>-323.0383822920033</v>
+      </c>
+      <c r="Q53">
+        <v>-20.33838229200336</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1203666680105671</v>
+      </c>
+      <c r="T53">
+        <v>1.489353196599911</v>
+      </c>
+      <c r="U53">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V53">
+        <v>0.04787582225750136</v>
+      </c>
+      <c r="W53">
+        <v>0.2335848895291351</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.17824207839725</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1801732637683247</v>
+      </c>
+      <c r="C54">
+        <v>-249.2034848308106</v>
+      </c>
+      <c r="D54">
+        <v>1984.56051516919</v>
+      </c>
+      <c r="E54">
+        <v>2233.764</v>
+      </c>
+      <c r="F54">
+        <v>2233.764</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>4295.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>398.5</v>
+      </c>
+      <c r="K54">
+        <v>302.7</v>
+      </c>
+      <c r="L54">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M54">
+        <v>548.0099438408257</v>
+      </c>
+      <c r="N54">
+        <v>-452.2099438408257</v>
+      </c>
+      <c r="O54">
+        <v>-121.4635909156458</v>
+      </c>
+      <c r="P54">
+        <v>-330.7463529251799</v>
+      </c>
+      <c r="Q54">
+        <v>-28.04635292517992</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1220659735941206</v>
+      </c>
+      <c r="T54">
+        <v>1.520381388195742</v>
+      </c>
+      <c r="U54">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V54">
+        <v>0.04695513336793402</v>
+      </c>
+      <c r="W54">
+        <v>0.2338107623906669</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1748143461203798</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1822385665516126</v>
+      </c>
+      <c r="C55">
+        <v>-313.8826871019153</v>
+      </c>
+      <c r="D55">
+        <v>1962.838312898085</v>
+      </c>
+      <c r="E55">
+        <v>2276.721</v>
+      </c>
+      <c r="F55">
+        <v>2276.721</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>4295.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>398.5</v>
+      </c>
+      <c r="K55">
+        <v>302.7</v>
+      </c>
+      <c r="L55">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M55">
+        <v>558.5485966069954</v>
+      </c>
+      <c r="N55">
+        <v>-462.7485966069954</v>
+      </c>
+      <c r="O55">
+        <v>-124.294273048639</v>
+      </c>
+      <c r="P55">
+        <v>-338.4543235583564</v>
+      </c>
+      <c r="Q55">
+        <v>-35.75432355835642</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.12383759005357</v>
+      </c>
+      <c r="T55">
+        <v>1.55272992837012</v>
+      </c>
+      <c r="U55">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V55">
+        <v>0.0460691874553315</v>
+      </c>
+      <c r="W55">
+        <v>0.23402811174799</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.171515962231316</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1843038693349004</v>
+      </c>
+      <c r="C56">
+        <v>-378.0915129226769</v>
+      </c>
+      <c r="D56">
+        <v>1941.586487077323</v>
+      </c>
+      <c r="E56">
+        <v>2319.678</v>
+      </c>
+      <c r="F56">
+        <v>2319.678</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>4295.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>398.5</v>
+      </c>
+      <c r="K56">
+        <v>302.7</v>
+      </c>
+      <c r="L56">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M56">
+        <v>569.0872493731652</v>
+      </c>
+      <c r="N56">
+        <v>-473.2872493731651</v>
+      </c>
+      <c r="O56">
+        <v>-127.1249551816322</v>
+      </c>
+      <c r="P56">
+        <v>-346.162294191533</v>
+      </c>
+      <c r="Q56">
+        <v>-43.46229419153298</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1256862333156041</v>
+      </c>
+      <c r="T56">
+        <v>1.586484926812948</v>
+      </c>
+      <c r="U56">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V56">
+        <v>0.04521605435430683</v>
+      </c>
+      <c r="W56">
+        <v>0.2342374111291158</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1683397407085139</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1863691721181883</v>
+      </c>
+      <c r="C57">
+        <v>-441.8450770676693</v>
+      </c>
+      <c r="D57">
+        <v>1920.789922932331</v>
+      </c>
+      <c r="E57">
+        <v>2362.635</v>
+      </c>
+      <c r="F57">
+        <v>2362.635</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>4295.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>398.5</v>
+      </c>
+      <c r="K57">
+        <v>302.7</v>
+      </c>
+      <c r="L57">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M57">
+        <v>579.6259021393349</v>
+      </c>
+      <c r="N57">
+        <v>-483.8259021393349</v>
+      </c>
+      <c r="O57">
+        <v>-129.9556373146254</v>
+      </c>
+      <c r="P57">
+        <v>-353.8702648247096</v>
+      </c>
+      <c r="Q57">
+        <v>-51.17026482470959</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1276170385003953</v>
+      </c>
+      <c r="T57">
+        <v>1.621740147408792</v>
+      </c>
+      <c r="U57">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V57">
+        <v>0.04439394427513761</v>
+      </c>
+      <c r="W57">
+        <v>0.2344390996236553</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1652790181501773</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1884344749014762</v>
+      </c>
+      <c r="C58">
+        <v>-505.1578535897072</v>
+      </c>
+      <c r="D58">
+        <v>1900.434146410293</v>
+      </c>
+      <c r="E58">
+        <v>2405.592</v>
+      </c>
+      <c r="F58">
+        <v>2405.592</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>4295.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>398.5</v>
+      </c>
+      <c r="K58">
+        <v>302.7</v>
+      </c>
+      <c r="L58">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M58">
+        <v>590.1645549055046</v>
+      </c>
+      <c r="N58">
+        <v>-494.3645549055046</v>
+      </c>
+      <c r="O58">
+        <v>-132.7863194476185</v>
+      </c>
+      <c r="P58">
+        <v>-361.5782354578861</v>
+      </c>
+      <c r="Q58">
+        <v>-58.87823545788609</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1296356075572225</v>
+      </c>
+      <c r="T58">
+        <v>1.658597878031719</v>
+      </c>
+      <c r="U58">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V58">
+        <v>0.04360119527022445</v>
+      </c>
+      <c r="W58">
+        <v>0.2346335849576755</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1623276071117813</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1904997776847641</v>
+      </c>
+      <c r="C59">
+        <v>-568.0437094144149</v>
+      </c>
+      <c r="D59">
+        <v>1880.505290585585</v>
+      </c>
+      <c r="E59">
+        <v>2448.549</v>
+      </c>
+      <c r="F59">
+        <v>2448.549</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>4295.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>398.5</v>
+      </c>
+      <c r="K59">
+        <v>302.7</v>
+      </c>
+      <c r="L59">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M59">
+        <v>600.7032076716744</v>
+      </c>
+      <c r="N59">
+        <v>-504.9032076716744</v>
+      </c>
+      <c r="O59">
+        <v>-135.6170015806117</v>
+      </c>
+      <c r="P59">
+        <v>-369.2862060910626</v>
+      </c>
+      <c r="Q59">
+        <v>-66.58620609106259</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1317480635469253</v>
+      </c>
+      <c r="T59">
+        <v>1.697169921706875</v>
+      </c>
+      <c r="U59">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V59">
+        <v>0.04283626201986963</v>
+      </c>
+      <c r="W59">
+        <v>0.234821246244888</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1594797543554343</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1925650804680519</v>
+      </c>
+      <c r="C60">
+        <v>-630.515935842993</v>
+      </c>
+      <c r="D60">
+        <v>1860.990064157007</v>
+      </c>
+      <c r="E60">
+        <v>2491.506</v>
+      </c>
+      <c r="F60">
+        <v>2491.506</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>4295.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>398.5</v>
+      </c>
+      <c r="K60">
+        <v>302.7</v>
+      </c>
+      <c r="L60">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M60">
+        <v>611.241860437844</v>
+      </c>
+      <c r="N60">
+        <v>-515.4418604378441</v>
+      </c>
+      <c r="O60">
+        <v>-138.4476837136049</v>
+      </c>
+      <c r="P60">
+        <v>-376.9941767242391</v>
+      </c>
+      <c r="Q60">
+        <v>-74.29417672423915</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.133961112678995</v>
+      </c>
+      <c r="T60">
+        <v>1.737578729366562</v>
+      </c>
+      <c r="U60">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V60">
+        <v>0.04209770577814775</v>
+      </c>
+      <c r="W60">
+        <v>0.2350024364532311</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1567301034182714</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1946303832513398</v>
+      </c>
+      <c r="C61">
+        <v>-692.5872781135856</v>
+      </c>
+      <c r="D61">
+        <v>1841.875721886414</v>
+      </c>
+      <c r="E61">
+        <v>2534.463</v>
+      </c>
+      <c r="F61">
+        <v>2534.463</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>4295.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>398.5</v>
+      </c>
+      <c r="K61">
+        <v>302.7</v>
+      </c>
+      <c r="L61">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M61">
+        <v>621.7805132040137</v>
+      </c>
+      <c r="N61">
+        <v>-525.9805132040137</v>
+      </c>
+      <c r="O61">
+        <v>-141.2783658465981</v>
+      </c>
+      <c r="P61">
+        <v>-384.7021473574156</v>
+      </c>
+      <c r="Q61">
+        <v>-82.00214735741565</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1362821154272631</v>
+      </c>
+      <c r="T61">
+        <v>1.779958698375503</v>
+      </c>
+      <c r="U61">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V61">
+        <v>0.04138418534122999</v>
+      </c>
+      <c r="W61">
+        <v>0.2351774846206134</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1540736609874533</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1966956860346277</v>
+      </c>
+      <c r="C62">
+        <v>-754.2699631594121</v>
+      </c>
+      <c r="D62">
+        <v>1823.150036840588</v>
+      </c>
+      <c r="E62">
+        <v>2577.42</v>
+      </c>
+      <c r="F62">
+        <v>2577.42</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>4295.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>398.5</v>
+      </c>
+      <c r="K62">
+        <v>302.7</v>
+      </c>
+      <c r="L62">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M62">
+        <v>632.3191659701835</v>
+      </c>
+      <c r="N62">
+        <v>-536.5191659701834</v>
+      </c>
+      <c r="O62">
+        <v>-144.1090479795913</v>
+      </c>
+      <c r="P62">
+        <v>-392.4101179905921</v>
+      </c>
+      <c r="Q62">
+        <v>-89.71011799059215</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1387191683129447</v>
+      </c>
+      <c r="T62">
+        <v>1.824457665834891</v>
+      </c>
+      <c r="U62">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V62">
+        <v>0.04069444891887616</v>
+      </c>
+      <c r="W62">
+        <v>0.235346697849083</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1515057666376626</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1987609888179155</v>
+      </c>
+      <c r="C63">
+        <v>-815.5757256906913</v>
+      </c>
+      <c r="D63">
+        <v>1804.801274309309</v>
+      </c>
+      <c r="E63">
+        <v>2620.377</v>
+      </c>
+      <c r="F63">
+        <v>2620.377</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>4295.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>398.5</v>
+      </c>
+      <c r="K63">
+        <v>302.7</v>
+      </c>
+      <c r="L63">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M63">
+        <v>642.8578187363532</v>
+      </c>
+      <c r="N63">
+        <v>-547.0578187363533</v>
+      </c>
+      <c r="O63">
+        <v>-146.9397301125845</v>
+      </c>
+      <c r="P63">
+        <v>-400.1180886237688</v>
+      </c>
+      <c r="Q63">
+        <v>-97.41808862376882</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1412811982696869</v>
+      </c>
+      <c r="T63">
+        <v>1.871238631625529</v>
+      </c>
+      <c r="U63">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V63">
+        <v>0.04002732680545195</v>
+      </c>
+      <c r="W63">
+        <v>0.2355103631028486</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1490220655452418</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2008262916012034</v>
+      </c>
+      <c r="C64">
+        <v>-876.5158327172865</v>
+      </c>
+      <c r="D64">
+        <v>1786.818167282713</v>
+      </c>
+      <c r="E64">
+        <v>2663.334</v>
+      </c>
+      <c r="F64">
+        <v>2663.334</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>4295.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>398.5</v>
+      </c>
+      <c r="K64">
+        <v>302.7</v>
+      </c>
+      <c r="L64">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M64">
+        <v>653.3964715025229</v>
+      </c>
+      <c r="N64">
+        <v>-557.5964715025229</v>
+      </c>
+      <c r="O64">
+        <v>-149.7704122455777</v>
+      </c>
+      <c r="P64">
+        <v>-407.8260592569453</v>
+      </c>
+      <c r="Q64">
+        <v>-105.1260592569453</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1439780719083628</v>
+      </c>
+      <c r="T64">
+        <v>1.920481753510411</v>
+      </c>
+      <c r="U64">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V64">
+        <v>0.03938172476020273</v>
+      </c>
+      <c r="W64">
+        <v>0.2356687488322993</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1466184838428991</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2028915943844913</v>
+      </c>
+      <c r="C65">
+        <v>-937.1011066197436</v>
+      </c>
+      <c r="D65">
+        <v>1769.189893380256</v>
+      </c>
+      <c r="E65">
+        <v>2706.291</v>
+      </c>
+      <c r="F65">
+        <v>2706.291</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>4295.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>398.5</v>
+      </c>
+      <c r="K65">
+        <v>302.7</v>
+      </c>
+      <c r="L65">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M65">
+        <v>663.9351242686926</v>
+      </c>
+      <c r="N65">
+        <v>-568.1351242686926</v>
+      </c>
+      <c r="O65">
+        <v>-152.6010943785708</v>
+      </c>
+      <c r="P65">
+        <v>-415.5340298901218</v>
+      </c>
+      <c r="Q65">
+        <v>-112.8340298901218</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1468207225004808</v>
+      </c>
+      <c r="T65">
+        <v>1.97238666576745</v>
+      </c>
+      <c r="U65">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V65">
+        <v>0.03875661801797729</v>
+      </c>
+      <c r="W65">
+        <v>0.2358221064433547</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1442912063215833</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2049568971677792</v>
+      </c>
+      <c r="C66">
+        <v>-997.3419468679929</v>
+      </c>
+      <c r="D66">
+        <v>1751.906053132007</v>
+      </c>
+      <c r="E66">
+        <v>2749.248</v>
+      </c>
+      <c r="F66">
+        <v>2749.248</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>4295.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>398.5</v>
+      </c>
+      <c r="K66">
+        <v>302.7</v>
+      </c>
+      <c r="L66">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M66">
+        <v>674.4737770348625</v>
+      </c>
+      <c r="N66">
+        <v>-578.6737770348625</v>
+      </c>
+      <c r="O66">
+        <v>-155.4317765115641</v>
+      </c>
+      <c r="P66">
+        <v>-423.2420005232984</v>
+      </c>
+      <c r="Q66">
+        <v>-120.5420005232984</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1498212981254941</v>
+      </c>
+      <c r="T66">
+        <v>2.02717518426099</v>
+      </c>
+      <c r="U66">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V66">
+        <v>0.03815104586144639</v>
+      </c>
+      <c r="W66">
+        <v>0.2359706716290645</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1420366562228085</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2070221999510671</v>
+      </c>
+      <c r="C67">
+        <v>-1057.248350479303</v>
+      </c>
+      <c r="D67">
+        <v>1734.956649520697</v>
+      </c>
+      <c r="E67">
+        <v>2792.205</v>
+      </c>
+      <c r="F67">
+        <v>2792.205</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>4295.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>398.5</v>
+      </c>
+      <c r="K67">
+        <v>302.7</v>
+      </c>
+      <c r="L67">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M67">
+        <v>685.0124298010321</v>
+      </c>
+      <c r="N67">
+        <v>-589.2124298010322</v>
+      </c>
+      <c r="O67">
+        <v>-158.2624586445572</v>
+      </c>
+      <c r="P67">
+        <v>-430.9499711564749</v>
+      </c>
+      <c r="Q67">
+        <v>-128.2499711564749</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.152993335214794</v>
+      </c>
+      <c r="T67">
+        <v>2.085094475239875</v>
+      </c>
+      <c r="U67">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V67">
+        <v>0.03756410669434722</v>
+      </c>
+      <c r="W67">
+        <v>0.2361146655782911</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1398514768963037</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2090875027343549</v>
+      </c>
+      <c r="C68">
+        <v>-1116.829931300053</v>
+      </c>
+      <c r="D68">
+        <v>1718.332068699947</v>
+      </c>
+      <c r="E68">
+        <v>2835.162</v>
+      </c>
+      <c r="F68">
+        <v>2835.162</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>4295.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>398.5</v>
+      </c>
+      <c r="K68">
+        <v>302.7</v>
+      </c>
+      <c r="L68">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M68">
+        <v>695.5510825672018</v>
+      </c>
+      <c r="N68">
+        <v>-599.7510825672018</v>
+      </c>
+      <c r="O68">
+        <v>-161.0931407775504</v>
+      </c>
+      <c r="P68">
+        <v>-438.6579417896514</v>
+      </c>
+      <c r="Q68">
+        <v>-135.9579417896514</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1563519627211114</v>
+      </c>
+      <c r="T68">
+        <v>2.146420783335166</v>
+      </c>
+      <c r="U68">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V68">
+        <v>0.03699495356261469</v>
+      </c>
+      <c r="W68">
+        <v>0.2362542960745107</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1377325151251477</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2111528055176428</v>
+      </c>
+      <c r="C69">
+        <v>-1176.095938189456</v>
+      </c>
+      <c r="D69">
+        <v>1702.023061810544</v>
+      </c>
+      <c r="E69">
+        <v>2878.119</v>
+      </c>
+      <c r="F69">
+        <v>2878.119</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>4295.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>398.5</v>
+      </c>
+      <c r="K69">
+        <v>302.7</v>
+      </c>
+      <c r="L69">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M69">
+        <v>706.0897353333717</v>
+      </c>
+      <c r="N69">
+        <v>-610.2897353333717</v>
+      </c>
+      <c r="O69">
+        <v>-163.9238229105436</v>
+      </c>
+      <c r="P69">
+        <v>-446.365912422828</v>
+      </c>
+      <c r="Q69">
+        <v>-143.6659124228281</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1599141434096299</v>
+      </c>
+      <c r="T69">
+        <v>2.211463837375625</v>
+      </c>
+      <c r="U69">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V69">
+        <v>0.0364427900766055</v>
+      </c>
+      <c r="W69">
+        <v>0.2363897584962163</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1356768059441753</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2132181083009307</v>
+      </c>
+      <c r="C70">
+        <v>-1235.055272177517</v>
+      </c>
+      <c r="D70">
+        <v>1686.020727822483</v>
+      </c>
+      <c r="E70">
+        <v>2921.076</v>
+      </c>
+      <c r="F70">
+        <v>2921.076</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>4295.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>398.5</v>
+      </c>
+      <c r="K70">
+        <v>302.7</v>
+      </c>
+      <c r="L70">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M70">
+        <v>716.6283880995413</v>
+      </c>
+      <c r="N70">
+        <v>-620.8283880995414</v>
+      </c>
+      <c r="O70">
+        <v>-166.7545050435368</v>
+      </c>
+      <c r="P70">
+        <v>-454.0738830560045</v>
+      </c>
+      <c r="Q70">
+        <v>-151.3738830560046</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1636989603911809</v>
+      </c>
+      <c r="T70">
+        <v>2.280572082293614</v>
+      </c>
+      <c r="U70">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V70">
+        <v>0.03590686669312601</v>
+      </c>
+      <c r="W70">
+        <v>0.2365212367290482</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1336815587979374</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2152834110842186</v>
+      </c>
+      <c r="C71">
+        <v>-1293.716502664092</v>
+      </c>
+      <c r="D71">
+        <v>1670.316497335908</v>
+      </c>
+      <c r="E71">
+        <v>2964.033</v>
+      </c>
+      <c r="F71">
+        <v>2964.033</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>4295.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>398.5</v>
+      </c>
+      <c r="K71">
+        <v>302.7</v>
+      </c>
+      <c r="L71">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M71">
+        <v>727.167040865711</v>
+      </c>
+      <c r="N71">
+        <v>-631.367040865711</v>
+      </c>
+      <c r="O71">
+        <v>-169.58518717653</v>
+      </c>
+      <c r="P71">
+        <v>-461.781853689181</v>
+      </c>
+      <c r="Q71">
+        <v>-159.0818536891811</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1677279591134771</v>
+      </c>
+      <c r="T71">
+        <v>2.354138923657924</v>
+      </c>
+      <c r="U71">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V71">
+        <v>0.03538647732076187</v>
+      </c>
+      <c r="W71">
+        <v>0.2366489039986097</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1317441449023151</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2173487138675064</v>
+      </c>
+      <c r="C72">
+        <v>-1352.087882720994</v>
+      </c>
+      <c r="D72">
+        <v>1654.902117279006</v>
+      </c>
+      <c r="E72">
+        <v>3006.99</v>
+      </c>
+      <c r="F72">
+        <v>3006.99</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>4295.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>398.5</v>
+      </c>
+      <c r="K72">
+        <v>302.7</v>
+      </c>
+      <c r="L72">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M72">
+        <v>737.7056936318808</v>
+      </c>
+      <c r="N72">
+        <v>-641.9056936318807</v>
+      </c>
+      <c r="O72">
+        <v>-172.4158693095231</v>
+      </c>
+      <c r="P72">
+        <v>-469.4898243223575</v>
+      </c>
+      <c r="Q72">
+        <v>-166.7898243223576</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.172025557750593</v>
+      </c>
+      <c r="T72">
+        <v>2.432610221113188</v>
+      </c>
+      <c r="U72">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V72">
+        <v>0.03488095621617956</v>
+      </c>
+      <c r="W72">
+        <v>0.2367729236318979</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.129862085689425</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2194140166507943</v>
+      </c>
+      <c r="C73">
+        <v>-1410.177363554567</v>
+      </c>
+      <c r="D73">
+        <v>1639.769636445433</v>
+      </c>
+      <c r="E73">
+        <v>3049.947</v>
+      </c>
+      <c r="F73">
+        <v>3049.947</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>4295.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>398.5</v>
+      </c>
+      <c r="K73">
+        <v>302.7</v>
+      </c>
+      <c r="L73">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M73">
+        <v>748.2443463980504</v>
+      </c>
+      <c r="N73">
+        <v>-652.4443463980504</v>
+      </c>
+      <c r="O73">
+        <v>-175.2465514425163</v>
+      </c>
+      <c r="P73">
+        <v>-477.1977949555341</v>
+      </c>
+      <c r="Q73">
+        <v>-174.4977949555341</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1766195425006134</v>
+      </c>
+      <c r="T73">
+        <v>2.516493332186056</v>
+      </c>
+      <c r="U73">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V73">
+        <v>0.03438967514271224</v>
+      </c>
+      <c r="W73">
+        <v>0.2368934497543893</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1280330422290107</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2214793194340822</v>
+      </c>
+      <c r="C74">
+        <v>-1467.992608181972</v>
+      </c>
+      <c r="D74">
+        <v>1624.911391818028</v>
+      </c>
+      <c r="E74">
+        <v>3092.904</v>
+      </c>
+      <c r="F74">
+        <v>3092.904</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>4295.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>398.5</v>
+      </c>
+      <c r="K74">
+        <v>302.7</v>
+      </c>
+      <c r="L74">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M74">
+        <v>758.7829991642201</v>
+      </c>
+      <c r="N74">
+        <v>-662.98299916422</v>
+      </c>
+      <c r="O74">
+        <v>-178.0772335755095</v>
+      </c>
+      <c r="P74">
+        <v>-484.9057655887106</v>
+      </c>
+      <c r="Q74">
+        <v>-182.2057655887106</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1815416690184924</v>
+      </c>
+      <c r="T74">
+        <v>2.606368094049844</v>
+      </c>
+      <c r="U74">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V74">
+        <v>0.03391204076573013</v>
+      </c>
+      <c r="W74">
+        <v>0.2370106279290337</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1262548055313856</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2235446222173701</v>
+      </c>
+      <c r="C75">
+        <v>-1525.541004370604</v>
+      </c>
+      <c r="D75">
+        <v>1610.319995629396</v>
+      </c>
+      <c r="E75">
+        <v>3135.861</v>
+      </c>
+      <c r="F75">
+        <v>3135.861</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>4295.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>398.5</v>
+      </c>
+      <c r="K75">
+        <v>302.7</v>
+      </c>
+      <c r="L75">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M75">
+        <v>769.3216519303899</v>
+      </c>
+      <c r="N75">
+        <v>-673.5216519303899</v>
+      </c>
+      <c r="O75">
+        <v>-180.9079157085027</v>
+      </c>
+      <c r="P75">
+        <v>-492.6137362218872</v>
+      </c>
+      <c r="Q75">
+        <v>-189.9137362218872</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1868283975006588</v>
+      </c>
+      <c r="T75">
+        <v>2.702900245681319</v>
+      </c>
+      <c r="U75">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V75">
+        <v>0.03344749226208999</v>
+      </c>
+      <c r="W75">
+        <v>0.237124595742729</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1245252876473938</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2256099250006579</v>
+      </c>
+      <c r="C76">
+        <v>-1582.829676886556</v>
+      </c>
+      <c r="D76">
+        <v>1595.988323113443</v>
+      </c>
+      <c r="E76">
+        <v>3178.818</v>
+      </c>
+      <c r="F76">
+        <v>3178.818</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>4295.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>398.5</v>
+      </c>
+      <c r="K76">
+        <v>302.7</v>
+      </c>
+      <c r="L76">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M76">
+        <v>779.8603046965596</v>
+      </c>
+      <c r="N76">
+        <v>-684.0603046965596</v>
+      </c>
+      <c r="O76">
+        <v>-183.7385978414959</v>
+      </c>
+      <c r="P76">
+        <v>-500.3217068550637</v>
+      </c>
+      <c r="Q76">
+        <v>-197.6217068550637</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1925217974045303</v>
+      </c>
+      <c r="T76">
+        <v>2.806857947438293</v>
+      </c>
+      <c r="U76">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V76">
+        <v>0.0329954991234131</v>
+      </c>
+      <c r="W76">
+        <v>0.2372354833452433</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1228425134899968</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2276752277839458</v>
+      </c>
+      <c r="C77">
+        <v>-1639.865499094802</v>
+      </c>
+      <c r="D77">
+        <v>1581.909500905198</v>
+      </c>
+      <c r="E77">
+        <v>3221.775</v>
+      </c>
+      <c r="F77">
+        <v>3221.775</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>4295.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>398.5</v>
+      </c>
+      <c r="K77">
+        <v>302.7</v>
+      </c>
+      <c r="L77">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M77">
+        <v>790.3989574627293</v>
+      </c>
+      <c r="N77">
+        <v>-694.5989574627292</v>
+      </c>
+      <c r="O77">
+        <v>-186.5692799744891</v>
+      </c>
+      <c r="P77">
+        <v>-508.0296774882402</v>
+      </c>
+      <c r="Q77">
+        <v>-205.3296774882402</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1986706693007116</v>
+      </c>
+      <c r="T77">
+        <v>2.919132265335825</v>
+      </c>
+      <c r="U77">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V77">
+        <v>0.03255555913510092</v>
+      </c>
+      <c r="W77">
+        <v>0.2373434139450239</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1212046133101301</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2297405305672337</v>
+      </c>
+      <c r="C78">
+        <v>-1696.655103950749</v>
+      </c>
+      <c r="D78">
+        <v>1568.076896049251</v>
+      </c>
+      <c r="E78">
+        <v>3264.732</v>
+      </c>
+      <c r="F78">
+        <v>3264.732</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>4295.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>398.5</v>
+      </c>
+      <c r="K78">
+        <v>302.7</v>
+      </c>
+      <c r="L78">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M78">
+        <v>800.9376102288991</v>
+      </c>
+      <c r="N78">
+        <v>-705.1376102288991</v>
+      </c>
+      <c r="O78">
+        <v>-189.3999621074823</v>
+      </c>
+      <c r="P78">
+        <v>-515.7376481214168</v>
+      </c>
+      <c r="Q78">
+        <v>-213.0376481214168</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2053319471882412</v>
+      </c>
+      <c r="T78">
+        <v>3.040762776391484</v>
+      </c>
+      <c r="U78">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V78">
+        <v>0.03212719651490223</v>
+      </c>
+      <c r="W78">
+        <v>0.2374485042658629</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1196098157665756</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2318058333505216</v>
+      </c>
+      <c r="C79">
+        <v>-1753.204894420136</v>
+      </c>
+      <c r="D79">
+        <v>1554.484105579864</v>
+      </c>
+      <c r="E79">
+        <v>3307.689</v>
+      </c>
+      <c r="F79">
+        <v>3307.689</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>4295.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>398.5</v>
+      </c>
+      <c r="K79">
+        <v>302.7</v>
+      </c>
+      <c r="L79">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M79">
+        <v>811.4762629950687</v>
+      </c>
+      <c r="N79">
+        <v>-715.6762629950688</v>
+      </c>
+      <c r="O79">
+        <v>-192.2306442404755</v>
+      </c>
+      <c r="P79">
+        <v>-523.4456187545933</v>
+      </c>
+      <c r="Q79">
+        <v>-220.7456187545933</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2125724666312082</v>
+      </c>
+      <c r="T79">
+        <v>3.172969853625897</v>
+      </c>
+      <c r="U79">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V79">
+        <v>0.03170996019652687</v>
+      </c>
+      <c r="W79">
+        <v>0.2375508649679788</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1180564415358408</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2338711361338094</v>
+      </c>
+      <c r="C80">
+        <v>-1809.521053361626</v>
+      </c>
+      <c r="D80">
+        <v>1541.124946638374</v>
+      </c>
+      <c r="E80">
+        <v>3350.646</v>
+      </c>
+      <c r="F80">
+        <v>3350.646</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>4295.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>398.5</v>
+      </c>
+      <c r="K80">
+        <v>302.7</v>
+      </c>
+      <c r="L80">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M80">
+        <v>822.0149157612386</v>
+      </c>
+      <c r="N80">
+        <v>-726.2149157612387</v>
+      </c>
+      <c r="O80">
+        <v>-195.0613263734687</v>
+      </c>
+      <c r="P80">
+        <v>-531.1535893877699</v>
+      </c>
+      <c r="Q80">
+        <v>-228.4535893877699</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.220471215114445</v>
+      </c>
+      <c r="T80">
+        <v>3.317195756063438</v>
+      </c>
+      <c r="U80">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V80">
+        <v>0.03130342224528934</v>
+      </c>
+      <c r="W80">
+        <v>0.2376506010367071</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1165428974135865</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2359364389170973</v>
+      </c>
+      <c r="C81">
+        <v>-1865.609552904167</v>
+      </c>
+      <c r="D81">
+        <v>1527.993447095833</v>
+      </c>
+      <c r="E81">
+        <v>3393.603</v>
+      </c>
+      <c r="F81">
+        <v>3393.603</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>4295.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>398.5</v>
+      </c>
+      <c r="K81">
+        <v>302.7</v>
+      </c>
+      <c r="L81">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M81">
+        <v>832.5535685274083</v>
+      </c>
+      <c r="N81">
+        <v>-736.7535685274083</v>
+      </c>
+      <c r="O81">
+        <v>-197.8920085064619</v>
+      </c>
+      <c r="P81">
+        <v>-538.8615600209464</v>
+      </c>
+      <c r="Q81">
+        <v>-236.1615600209464</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2291222253579899</v>
+      </c>
+      <c r="T81">
+        <v>3.475157458733125</v>
+      </c>
+      <c r="U81">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V81">
+        <v>0.03090717639408315</v>
+      </c>
+      <c r="W81">
+        <v>0.2377478121416702</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1150676708640475</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2380017417003852</v>
+      </c>
+      <c r="C82">
+        <v>-1921.476163348986</v>
+      </c>
+      <c r="D82">
+        <v>1515.083836651014</v>
+      </c>
+      <c r="E82">
+        <v>3436.56</v>
+      </c>
+      <c r="F82">
+        <v>3436.56</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>4295.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>398.5</v>
+      </c>
+      <c r="K82">
+        <v>302.7</v>
+      </c>
+      <c r="L82">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M82">
+        <v>843.0922212935779</v>
+      </c>
+      <c r="N82">
+        <v>-747.292221293578</v>
+      </c>
+      <c r="O82">
+        <v>-200.7226906394551</v>
+      </c>
+      <c r="P82">
+        <v>-546.5695306541229</v>
+      </c>
+      <c r="Q82">
+        <v>-243.8695306541229</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2386383366258894</v>
+      </c>
+      <c r="T82">
+        <v>3.648915331669782</v>
+      </c>
+      <c r="U82">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V82">
+        <v>0.03052083668915712</v>
+      </c>
+      <c r="W82">
+        <v>0.2378425929690091</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1136293249782468</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2400670444836731</v>
+      </c>
+      <c r="C83">
+        <v>-1977.126461624105</v>
+      </c>
+      <c r="D83">
+        <v>1502.390538375895</v>
+      </c>
+      <c r="E83">
+        <v>3479.517</v>
+      </c>
+      <c r="F83">
+        <v>3479.517</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>4295.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>398.5</v>
+      </c>
+      <c r="K83">
+        <v>302.7</v>
+      </c>
+      <c r="L83">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M83">
+        <v>853.6308740597478</v>
+      </c>
+      <c r="N83">
+        <v>-757.8308740597479</v>
+      </c>
+      <c r="O83">
+        <v>-203.5533727724483</v>
+      </c>
+      <c r="P83">
+        <v>-554.2775012872996</v>
+      </c>
+      <c r="Q83">
+        <v>-251.5775012872996</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2491561438167258</v>
+      </c>
+      <c r="T83">
+        <v>3.840963507020823</v>
+      </c>
+      <c r="U83">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V83">
+        <v>0.03014403623620455</v>
+      </c>
+      <c r="W83">
+        <v>0.2379350335290064</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1122264938056758</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.242132347266961</v>
+      </c>
+      <c r="C84">
+        <v>-2032.565839317396</v>
+      </c>
+      <c r="D84">
+        <v>1489.908160682605</v>
+      </c>
+      <c r="E84">
+        <v>3522.474</v>
+      </c>
+      <c r="F84">
+        <v>3522.474</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>4295.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>398.5</v>
+      </c>
+      <c r="K84">
+        <v>302.7</v>
+      </c>
+      <c r="L84">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M84">
+        <v>864.1695268259175</v>
+      </c>
+      <c r="N84">
+        <v>-768.3695268259175</v>
+      </c>
+      <c r="O84">
+        <v>-206.3840549054414</v>
+      </c>
+      <c r="P84">
+        <v>-561.9854719204761</v>
+      </c>
+      <c r="Q84">
+        <v>-259.2854719204761</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2608425962509883</v>
+      </c>
+      <c r="T84">
+        <v>4.05435036852198</v>
+      </c>
+      <c r="U84">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V84">
+        <v>0.02977642603820206</v>
+      </c>
+      <c r="W84">
+        <v>0.2380252194411988</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1108578780275579</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2441976500502488</v>
+      </c>
+      <c r="C85">
+        <v>-2087.799510312487</v>
+      </c>
+      <c r="D85">
+        <v>1477.631489687513</v>
+      </c>
+      <c r="E85">
+        <v>3565.431</v>
+      </c>
+      <c r="F85">
+        <v>3565.431</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>4295.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>398.5</v>
+      </c>
+      <c r="K85">
+        <v>302.7</v>
+      </c>
+      <c r="L85">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M85">
+        <v>874.7081795920872</v>
+      </c>
+      <c r="N85">
+        <v>-778.9081795920872</v>
+      </c>
+      <c r="O85">
+        <v>-209.2147370384346</v>
+      </c>
+      <c r="P85">
+        <v>-569.6934425536526</v>
+      </c>
+      <c r="Q85">
+        <v>-266.9934425536526</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2739039254422229</v>
+      </c>
+      <c r="T85">
+        <v>4.292841566670332</v>
+      </c>
+      <c r="U85">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V85">
+        <v>0.02941767391725987</v>
+      </c>
+      <c r="W85">
+        <v>0.2381132321988806</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1095222409428885</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2462629528335367</v>
+      </c>
+      <c r="C86">
+        <v>-2142.832518050243</v>
+      </c>
+      <c r="D86">
+        <v>1465.555481949757</v>
+      </c>
+      <c r="E86">
+        <v>3608.388</v>
+      </c>
+      <c r="F86">
+        <v>3608.388</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>4295.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>398.5</v>
+      </c>
+      <c r="K86">
+        <v>302.7</v>
+      </c>
+      <c r="L86">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M86">
+        <v>885.2468323582569</v>
+      </c>
+      <c r="N86">
+        <v>-789.4468323582569</v>
+      </c>
+      <c r="O86">
+        <v>-212.0454191714278</v>
+      </c>
+      <c r="P86">
+        <v>-577.4014131868291</v>
+      </c>
+      <c r="Q86">
+        <v>-274.7014131868291</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2885979207823617</v>
+      </c>
+      <c r="T86">
+        <v>4.561144164587225</v>
+      </c>
+      <c r="U86">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V86">
+        <v>0.02906746351348296</v>
+      </c>
+      <c r="W86">
+        <v>0.2381991494147128</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1082184047411876</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2483282556168246</v>
+      </c>
+      <c r="C87">
+        <v>-2197.669742437062</v>
+      </c>
+      <c r="D87">
+        <v>1453.675257562938</v>
+      </c>
+      <c r="E87">
+        <v>3651.345</v>
+      </c>
+      <c r="F87">
+        <v>3651.345</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>4295.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>398.5</v>
+      </c>
+      <c r="K87">
+        <v>302.7</v>
+      </c>
+      <c r="L87">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M87">
+        <v>895.7854851244266</v>
+      </c>
+      <c r="N87">
+        <v>-799.9854851244265</v>
+      </c>
+      <c r="O87">
+        <v>-214.876101304421</v>
+      </c>
+      <c r="P87">
+        <v>-585.1093838200055</v>
+      </c>
+      <c r="Q87">
+        <v>-282.4093838200055</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3052511155011859</v>
+      </c>
+      <c r="T87">
+        <v>4.865220442226375</v>
+      </c>
+      <c r="U87">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V87">
+        <v>0.02872549335450081</v>
+      </c>
+      <c r="W87">
+        <v>0.2382830450489961</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1069452470383501</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2503935584001125</v>
+      </c>
+      <c r="C88">
+        <v>-2252.315906419862</v>
+      </c>
+      <c r="D88">
+        <v>1441.986093580138</v>
+      </c>
+      <c r="E88">
+        <v>3694.302</v>
+      </c>
+      <c r="F88">
+        <v>3694.302</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>4295.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>398.5</v>
+      </c>
+      <c r="K88">
+        <v>302.7</v>
+      </c>
+      <c r="L88">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M88">
+        <v>906.3241378905963</v>
+      </c>
+      <c r="N88">
+        <v>-810.5241378905962</v>
+      </c>
+      <c r="O88">
+        <v>-217.7067834374141</v>
+      </c>
+      <c r="P88">
+        <v>-592.817354453182</v>
+      </c>
+      <c r="Q88">
+        <v>-290.117354453182</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3242833380369849</v>
+      </c>
+      <c r="T88">
+        <v>5.212736188099687</v>
+      </c>
+      <c r="U88">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V88">
+        <v>0.0283914759899136</v>
+      </c>
+      <c r="W88">
+        <v>0.2383649896220169</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1057016976541832</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2524588611834003</v>
+      </c>
+      <c r="C89">
+        <v>-2306.775582246395</v>
+      </c>
+      <c r="D89">
+        <v>1430.483417753605</v>
+      </c>
+      <c r="E89">
+        <v>3737.259</v>
+      </c>
+      <c r="F89">
+        <v>3737.259</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>4295.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>398.5</v>
+      </c>
+      <c r="K89">
+        <v>302.7</v>
+      </c>
+      <c r="L89">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M89">
+        <v>916.862790656766</v>
+      </c>
+      <c r="N89">
+        <v>-821.0627906567661</v>
+      </c>
+      <c r="O89">
+        <v>-220.5374655704074</v>
+      </c>
+      <c r="P89">
+        <v>-600.5253250863587</v>
+      </c>
+      <c r="Q89">
+        <v>-297.8253250863588</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3462435948090606</v>
+      </c>
+      <c r="T89">
+        <v>5.613715894876586</v>
+      </c>
+      <c r="U89">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V89">
+        <v>0.02806513718543183</v>
+      </c>
+      <c r="W89">
+        <v>0.2384450504117499</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.104486735612181</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2545241639666882</v>
+      </c>
+      <c r="C90">
+        <v>-2361.053197428285</v>
+      </c>
+      <c r="D90">
+        <v>1419.162802571715</v>
+      </c>
+      <c r="E90">
+        <v>3780.216</v>
+      </c>
+      <c r="F90">
+        <v>3780.216</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>4295.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>398.5</v>
+      </c>
+      <c r="K90">
+        <v>302.7</v>
+      </c>
+      <c r="L90">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M90">
+        <v>927.4014434229358</v>
+      </c>
+      <c r="N90">
+        <v>-831.6014434229357</v>
+      </c>
+      <c r="O90">
+        <v>-223.3681477034006</v>
+      </c>
+      <c r="P90">
+        <v>-608.2332957195351</v>
+      </c>
+      <c r="Q90">
+        <v>-305.5332957195351</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3718638943764823</v>
+      </c>
+      <c r="T90">
+        <v>6.081525552782968</v>
+      </c>
+      <c r="U90">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V90">
+        <v>0.02774621517196101</v>
+      </c>
+      <c r="W90">
+        <v>0.2385232916380799</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1032993863438608</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2565894667499761</v>
+      </c>
+      <c r="C91">
+        <v>-2415.153040423152</v>
+      </c>
+      <c r="D91">
+        <v>1408.019959576848</v>
+      </c>
+      <c r="E91">
+        <v>3823.173</v>
+      </c>
+      <c r="F91">
+        <v>3823.173</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>4295.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>398.5</v>
+      </c>
+      <c r="K91">
+        <v>302.7</v>
+      </c>
+      <c r="L91">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M91">
+        <v>937.9400961891055</v>
+      </c>
+      <c r="N91">
+        <v>-842.1400961891054</v>
+      </c>
+      <c r="O91">
+        <v>-226.1988298363937</v>
+      </c>
+      <c r="P91">
+        <v>-615.9412663527116</v>
+      </c>
+      <c r="Q91">
+        <v>-313.2412663527116</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4021424302288899</v>
+      </c>
+      <c r="T91">
+        <v>6.634391512126876</v>
+      </c>
+      <c r="U91">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V91">
+        <v>0.02743445994530977</v>
+      </c>
+      <c r="W91">
+        <v>0.2385997746346047</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1021387190815704</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2586547695332639</v>
+      </c>
+      <c r="C92">
+        <v>-2469.07926605114</v>
+      </c>
+      <c r="D92">
+        <v>1397.050733948861</v>
+      </c>
+      <c r="E92">
+        <v>3866.13</v>
+      </c>
+      <c r="F92">
+        <v>3866.13</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>4295.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>398.5</v>
+      </c>
+      <c r="K92">
+        <v>302.7</v>
+      </c>
+      <c r="L92">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M92">
+        <v>948.4787489552753</v>
+      </c>
+      <c r="N92">
+        <v>-852.6787489552753</v>
+      </c>
+      <c r="O92">
+        <v>-229.029511969387</v>
+      </c>
+      <c r="P92">
+        <v>-623.6492369858884</v>
+      </c>
+      <c r="Q92">
+        <v>-320.9492369858884</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4384766732517789</v>
+      </c>
+      <c r="T92">
+        <v>7.297830663339563</v>
+      </c>
+      <c r="U92">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V92">
+        <v>0.0271296326125841</v>
+      </c>
+      <c r="W92">
+        <v>0.2386745580089845</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1010038444251082</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2607200723165518</v>
+      </c>
+      <c r="C93">
+        <v>-2522.835900660206</v>
+      </c>
+      <c r="D93">
+        <v>1386.251099339794</v>
+      </c>
+      <c r="E93">
+        <v>3909.087</v>
+      </c>
+      <c r="F93">
+        <v>3909.087</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>4295.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>398.5</v>
+      </c>
+      <c r="K93">
+        <v>302.7</v>
+      </c>
+      <c r="L93">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M93">
+        <v>959.017401721445</v>
+      </c>
+      <c r="N93">
+        <v>-863.217401721445</v>
+      </c>
+      <c r="O93">
+        <v>-231.8601941023801</v>
+      </c>
+      <c r="P93">
+        <v>-631.3572076190649</v>
+      </c>
+      <c r="Q93">
+        <v>-328.6572076190649</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4828851925019765</v>
+      </c>
+      <c r="T93">
+        <v>8.108700737043959</v>
+      </c>
+      <c r="U93">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V93">
+        <v>0.02683150478167658</v>
+      </c>
+      <c r="W93">
+        <v>0.2387476977927186</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.0998939120687885</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2627853750998397</v>
+      </c>
+      <c r="C94">
+        <v>-2576.426847053687</v>
+      </c>
+      <c r="D94">
+        <v>1375.617152946312</v>
+      </c>
+      <c r="E94">
+        <v>3952.044</v>
+      </c>
+      <c r="F94">
+        <v>3952.044</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>4295.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>398.5</v>
+      </c>
+      <c r="K94">
+        <v>302.7</v>
+      </c>
+      <c r="L94">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M94">
+        <v>969.5560544876147</v>
+      </c>
+      <c r="N94">
+        <v>-873.7560544876146</v>
+      </c>
+      <c r="O94">
+        <v>-234.6908762353733</v>
+      </c>
+      <c r="P94">
+        <v>-639.0651782522414</v>
+      </c>
+      <c r="Q94">
+        <v>-336.3651782522414</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5383958415647239</v>
+      </c>
+      <c r="T94">
+        <v>9.122288329174459</v>
+      </c>
+      <c r="U94">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V94">
+        <v>0.0265398579905714</v>
+      </c>
+      <c r="W94">
+        <v>0.2388192475811541</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.09880810867673651</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2648506778831276</v>
+      </c>
+      <c r="C95">
+        <v>-2629.855889192778</v>
+      </c>
+      <c r="D95">
+        <v>1365.145110807222</v>
+      </c>
+      <c r="E95">
+        <v>3995.001</v>
+      </c>
+      <c r="F95">
+        <v>3995.001</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>4295.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>398.5</v>
+      </c>
+      <c r="K95">
+        <v>302.7</v>
+      </c>
+      <c r="L95">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M95">
+        <v>980.0947072537845</v>
+      </c>
+      <c r="N95">
+        <v>-884.2947072537845</v>
+      </c>
+      <c r="O95">
+        <v>-237.5215583683665</v>
+      </c>
+      <c r="P95">
+        <v>-646.773148885418</v>
+      </c>
+      <c r="Q95">
+        <v>-344.073148885418</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6097666760739702</v>
+      </c>
+      <c r="T95">
+        <v>10.42547237619938</v>
+      </c>
+      <c r="U95">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V95">
+        <v>0.02625448317346848</v>
+      </c>
+      <c r="W95">
+        <v>0.238889258664462</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.09774565589526607</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2669159806664154</v>
+      </c>
+      <c r="C96">
+        <v>-2683.126696685857</v>
+      </c>
+      <c r="D96">
+        <v>1354.831303314144</v>
+      </c>
+      <c r="E96">
+        <v>4037.958</v>
+      </c>
+      <c r="F96">
+        <v>4037.958</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>4295.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>398.5</v>
+      </c>
+      <c r="K96">
+        <v>302.7</v>
+      </c>
+      <c r="L96">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M96">
+        <v>990.6333600199541</v>
+      </c>
+      <c r="N96">
+        <v>-894.8333600199542</v>
+      </c>
+      <c r="O96">
+        <v>-240.3522405013597</v>
+      </c>
+      <c r="P96">
+        <v>-654.4811195185945</v>
+      </c>
+      <c r="Q96">
+        <v>-351.7811195185945</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7049277887529652</v>
+      </c>
+      <c r="T96">
+        <v>12.16305110556595</v>
+      </c>
+      <c r="U96">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V96">
+        <v>0.02597518016098478</v>
+      </c>
+      <c r="W96">
+        <v>0.2389577801502527</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.09670580849212496</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2689812834497033</v>
+      </c>
+      <c r="C97">
+        <v>-2736.242829075826</v>
+      </c>
+      <c r="D97">
+        <v>1344.672170924174</v>
+      </c>
+      <c r="E97">
+        <v>4080.915</v>
+      </c>
+      <c r="F97">
+        <v>4080.915</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>4295.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>398.5</v>
+      </c>
+      <c r="K97">
+        <v>302.7</v>
+      </c>
+      <c r="L97">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M97">
+        <v>1001.172012786124</v>
+      </c>
+      <c r="N97">
+        <v>-905.3720127861238</v>
+      </c>
+      <c r="O97">
+        <v>-243.1829226343529</v>
+      </c>
+      <c r="P97">
+        <v>-662.189090151771</v>
+      </c>
+      <c r="Q97">
+        <v>-359.489090151771</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8381533465035589</v>
+      </c>
+      <c r="T97">
+        <v>14.59566132667915</v>
+      </c>
+      <c r="U97">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V97">
+        <v>0.02570175721192178</v>
+      </c>
+      <c r="W97">
+        <v>0.2390248590784478</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.09568785261326063</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2710465862329912</v>
+      </c>
+      <c r="C98">
+        <v>-2789.207739936008</v>
+      </c>
+      <c r="D98">
+        <v>1334.664260063991</v>
+      </c>
+      <c r="E98">
+        <v>4123.871999999999</v>
+      </c>
+      <c r="F98">
+        <v>4123.871999999999</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>4295.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>398.5</v>
+      </c>
+      <c r="K98">
+        <v>302.7</v>
+      </c>
+      <c r="L98">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M98">
+        <v>1011.710665552293</v>
+      </c>
+      <c r="N98">
+        <v>-915.9106655522935</v>
+      </c>
+      <c r="O98">
+        <v>-246.013604767346</v>
+      </c>
+      <c r="P98">
+        <v>-669.8970607849475</v>
+      </c>
+      <c r="Q98">
+        <v>-367.1970607849475</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.037991683129446</v>
+      </c>
+      <c r="T98">
+        <v>18.24457665834889</v>
+      </c>
+      <c r="U98">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V98">
+        <v>0.0254340305742976</v>
+      </c>
+      <c r="W98">
+        <v>0.2390905405289722</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.09469110414853898</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.273111889016279</v>
+      </c>
+      <c r="C99">
+        <v>-2842.02478078447</v>
+      </c>
+      <c r="D99">
+        <v>1324.80421921553</v>
+      </c>
+      <c r="E99">
+        <v>4166.829</v>
+      </c>
+      <c r="F99">
+        <v>4166.829</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>4295.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>398.5</v>
+      </c>
+      <c r="K99">
+        <v>302.7</v>
+      </c>
+      <c r="L99">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M99">
+        <v>1022.249318318463</v>
+      </c>
+      <c r="N99">
+        <v>-926.4493183184632</v>
+      </c>
+      <c r="O99">
+        <v>-248.8442869003392</v>
+      </c>
+      <c r="P99">
+        <v>-677.605031418124</v>
+      </c>
+      <c r="Q99">
+        <v>-374.905031418124</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.371055577505928</v>
+      </c>
+      <c r="T99">
+        <v>24.32610221113185</v>
+      </c>
+      <c r="U99">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V99">
+        <v>0.02517182407353164</v>
+      </c>
+      <c r="W99">
+        <v>0.2391548677227847</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.09371490719855424</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2751771917995669</v>
+      </c>
+      <c r="C100">
+        <v>-2894.697204826129</v>
+      </c>
+      <c r="D100">
+        <v>1315.088795173871</v>
+      </c>
+      <c r="E100">
+        <v>4209.786</v>
+      </c>
+      <c r="F100">
+        <v>4209.786</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>4295.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>398.5</v>
+      </c>
+      <c r="K100">
+        <v>302.7</v>
+      </c>
+      <c r="L100">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M100">
+        <v>1032.787971084633</v>
+      </c>
+      <c r="N100">
+        <v>-936.987971084633</v>
+      </c>
+      <c r="O100">
+        <v>-251.6749690333324</v>
+      </c>
+      <c r="P100">
+        <v>-685.3130020513006</v>
+      </c>
+      <c r="Q100">
+        <v>-382.6130020513006</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.037183366258893</v>
+      </c>
+      <c r="T100">
+        <v>36.48915331669778</v>
+      </c>
+      <c r="U100">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V100">
+        <v>0.02491496872584254</v>
+      </c>
+      <c r="W100">
+        <v>0.2392178821167235</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.09275863263530348</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2772424945828548</v>
+      </c>
+      <c r="C101">
+        <v>-2947.228170531395</v>
+      </c>
+      <c r="D101">
+        <v>1305.514829468604</v>
+      </c>
+      <c r="E101">
+        <v>4252.742999999999</v>
+      </c>
+      <c r="F101">
+        <v>4252.742999999999</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>4295.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>398.5</v>
+      </c>
+      <c r="K101">
+        <v>302.7</v>
+      </c>
+      <c r="L101">
+        <v>95.80000000000001</v>
+      </c>
+      <c r="M101">
+        <v>1043.326623850803</v>
+      </c>
+      <c r="N101">
+        <v>-947.5266238508027</v>
+      </c>
+      <c r="O101">
+        <v>-254.5056511663256</v>
+      </c>
+      <c r="P101">
+        <v>-693.0209726844771</v>
+      </c>
+      <c r="Q101">
+        <v>-390.3209726844771</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.035566732517785</v>
+      </c>
+      <c r="T101">
+        <v>72.97830663339556</v>
+      </c>
+      <c r="U101">
+        <v>0.2453302783287875</v>
+      </c>
+      <c r="V101">
+        <v>0.02466330237507646</v>
+      </c>
+      <c r="W101">
+        <v>0.239279623492603</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.09182167675009845</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
